--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,62 +555,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-gnistan/1631798921</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/bosnia-and-herzegovina-vs-qatar/1627256764</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-23 16:00</t>
+          <t>2026-06-24 19:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-23 15:44</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>1.370</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.940</t>
+          <t>5.600</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>8.750</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -620,12 +620,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -635,27 +635,27 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,107 +668,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/inter-turku-vs-sjk/1631805289</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-canada/1620858186</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-23 16:00</t>
+          <t>2026-06-24 19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.300</t>
+          <t>3.090</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.300</t>
+          <t>3.310</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,97 +781,97 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-hjk-helsinki/1631798940</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/morocco-vs-haiti/1631342070</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23 17:00</t>
+          <t>2026-06-24 22:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.120</t>
+          <t>1.190</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.970</t>
+          <t>7.750</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.336</t>
+          <t>17.750</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,85 +894,109 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-mikkelin-palloilijat/1632011661</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/scotland-vs-brazil/1620865469</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-26 16:00</t>
+          <t>2026-06-24 22:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>10.000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>5.850</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.830</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -983,85 +1007,109 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-sjk-akatemia/1632011760</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/czechia-vs-mexico/1631338312</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-26 16:00</t>
+          <t>2026-06-25 01:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>3.780</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.990</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3.580</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3.610</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1072,85 +1120,109 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/brage-vs-falkenbergs/1632018127</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-south-korea/1620834899</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-26 17:00</t>
+          <t>2026-06-25 01:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.430</t>
+          <t>6.130</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>4.080</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.750</t>
+          <t>1.621</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1161,67 +1233,79 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-osters/1632042019</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ecuador-vs-germany/1620858182</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-25 20:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>4.290</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -1229,17 +1313,29 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1250,85 +1346,109 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-orebro-sk/1632034515</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/curacao-vs-ivory-coast/1631342068</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-25 20:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Curacao</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orebro SK</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>16.690</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.920</t>
+          <t>7.930</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>1.146</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>+4.5</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1339,85 +1459,109 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/tunisia-vs-netherlands/1620849622</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-25 23:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>21.730</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>10.560</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.490</t>
+          <t>1.096</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1428,85 +1572,109 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/japan-vs-sweden/1631338310</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-25 23:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.820</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1517,62 +1685,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-londrina/1631994037</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-25 23:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>5.410</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1580,17 +1748,17 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1606,52 +1774,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/turkiye-vs-usa/1631350202</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-26 02:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Turkiye</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.740</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>4.160</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1661,30 +1829,54 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1695,85 +1887,109 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-australia/1620858183</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-26 02:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>2.780</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>2.240</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.220</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>1.699</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1784,47 +2000,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-kongsvinger/1632018178</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-sjk-akatemia/1632011760</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-26 16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1834,12 +2050,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1847,17 +2063,17 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -1873,62 +2089,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-hodd/1632018179</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-mikkelin-palloilijat/1632011661</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-26 16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.704</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.550</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.310</t>
+          <t>4.830</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1936,17 +2152,17 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1962,47 +2178,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/brage-vs-falkenbergs/1632018127</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-26 17:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.480</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.690</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2012,12 +2228,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2025,7 +2241,7 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2035,7 +2251,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -2051,85 +2267,109 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-france/1631338309</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-26 19:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>4.700</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>4.330</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.671</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2140,85 +2380,109 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/senegal-vs-iraq/1631350200</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-26 19:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nordic United</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>6.820</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.640</t>
+          <t>12.460</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -2229,62 +2493,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stromsgodset-vs-odd-bk/1632022591</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-vila-nova/1632022596</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-26 22:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.606</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.480</t>
+          <t>3.180</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.520</t>
+          <t>4.360</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2292,17 +2556,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2318,67 +2582,79 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-fc-lahti/1631904343</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/cape-verde-vs-saudi-arabia/1631350201</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-27 18:00</t>
+          <t>2026-06-27 00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>2.510</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>2.880</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -2386,17 +2662,29 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2407,52 +2695,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sogndal-vs-egersunds/1632024906</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/uruguay-vs-spain/1631342071</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-27 18:00</t>
+          <t>2026-06-27 00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>7.350</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>4.130</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.680</t>
+          <t>1.502</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2462,30 +2750,54 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2496,52 +2808,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-27 03:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>15.090</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.670</t>
+          <t>7.560</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6.370</t>
+          <t>1.177</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2551,30 +2863,54 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -2585,85 +2921,109 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-27 03:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>2.490</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2.580</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3.830</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>3.690</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4.090</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -2674,62 +3034,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-japs/1632066271</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ilves-vs-sjk/1631895161</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-27 11:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>2.330</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.810</t>
+          <t>2.770</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2737,17 +3097,17 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2763,12 +3123,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-helsingborgs/1632066312</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-osters/1632042019</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-28 15:00</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2778,47 +3138,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-23 15:45</t>
+          <t>2026-06-24 16:16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.740</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>3.990</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2826,17 +3186,17 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
@@ -2849,6 +3209,3354 @@
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-orebro-sk/1632034515</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sweden - Superettan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ljungskile</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Orebro SK</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:16</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3.920</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3.570</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Finland - Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>JIPPO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EIF</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1.714</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3.760</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4.490</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-27 13:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Finland - Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FC Haka</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>KTP</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2.420</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.370</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2.820</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-27 14:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Finland - Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HJK Helsinki</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:16</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2.280</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>3.630</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2.980</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-27 14:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Finland - Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>IFK Mariehamn</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Inter Turku</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:16</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>8.710</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>5.420</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1.319</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-hodd/1632018179</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-27 14:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Hodd</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:17</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3.550</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3.310</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06-27 14:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sandnes Ulf</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Raufoss</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:17</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1.704</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>4.070</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4.260</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-kongsvinger/1632018178</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-27 14:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:17</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3.950</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3.170</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06-27 14:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Strommen</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:17</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2.520</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>3.800</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2.480</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-27 14:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Asane Fotball</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ranheim</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:17</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3.520</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>4.170</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-27 14:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Stabaek</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Bryne</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:17</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1.757</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>4.210</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3.820</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-america-mineiro/1632035579</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-27 14:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Operario Ferroviario</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>America Mineiro</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3.300</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4.470</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-27 15:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sweden - Superettan</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Nordic United</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Oddevold</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:16</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2.600</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3.360</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2.640</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06-27 15:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sweden - Superettan</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ostersunds FK</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:16</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3.770</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.360</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Finland - Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TPS</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Jaro</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:16</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2.170</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3.730</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3.100</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Finland - Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:16</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2.670</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3.370</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2.650</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stromsgodset-vs-odd-bk/1632022591</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-27 16:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Stromsgodset</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Odd BK</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:17</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1.606</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4.480</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4.520</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-fc-lahti/1631904343</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-06-27 18:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Finland - Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AC Oulu</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>FC Lahti</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:16</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3.640</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3.830</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sogndal-vs-egersunds/1632024906</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06-27 18:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sogndal</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Egersunds</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:17</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2.290</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3.960</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2.680</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sao-bernardo/1632048005</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-06-27 19:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sao Bernardo</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1.613</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3.640</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5.990</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FIFA - World Cup</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>3.250</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5.870</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FIFA - World Cup</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>15.480</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>8.180</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1.162</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>+2.25</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-portugal/1631338311</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-06-27 23:30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FIFA - World Cup</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>3.990</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3.790</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/dr-congo-vs-uzbekistan/1631342072</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-27 23:30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FIFA - World Cup</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DR Congo</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>4.230</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4.100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06-28 02:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FIFA - World Cup</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>13.740</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>7.400</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1.189</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>+1.75</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-06-28 02:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FIFA - World Cup</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>3.900</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2.170</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2.860</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1.645</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2.270</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06-28 13:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Sweden - Superettan</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Norrkoping</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Norrby</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:16</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1.436</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>4.640</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6.340</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06-28 13:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sweden - Superettan</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Landskrona</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Varnamo</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:16</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3.650</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4.020</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-japs/1632066271</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-06-28 13:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Finland - Ykkosliiga</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>KaPa</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>JaPS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:17</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2.450</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>3.320</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2.810</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-helsingborgs/1632066312</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Sweden - Superettan</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sandvikens IF</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Helsingborgs</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:16</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2.180</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>3.760</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2.970</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-28 19:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Atletico Goianiense</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.460</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>4.040</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7.640</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-28 19:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ceara</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>3.070</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3.960</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-28 19:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>3.380</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>4.020</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-06-28 21:30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Nautico</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>3.470</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4.380</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-06-28 21:30</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>3.310</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4.140</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-06-30 23:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-24 16:18</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2.780</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2.540</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3.330</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1.751</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,12 +555,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/bosnia-and-herzegovina-vs-qatar/1627256764</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ecuador-vs-germany/1620858182</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-24 19:00</t>
+          <t>2026-06-25 20:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -570,92 +570,92 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.370</t>
+          <t>5.500</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5.600</t>
+          <t>5.250</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.750</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,12 +668,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-canada/1620858186</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/curacao-vs-ivory-coast/1631342068</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-24 19:00</t>
+          <t>2026-06-25 20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -683,47 +683,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Curacao</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>17.000</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.090</t>
+          <t>8.250</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.310</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.130</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -733,42 +733,42 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>+4.5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>1.952</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.806</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,12 +781,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/morocco-vs-haiti/1631342070</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/japan-vs-sweden/1631338310</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-24 22:00</t>
+          <t>2026-06-25 23:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -796,74 +796,74 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.190</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7.750</t>
+          <t>3.550</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17.750</t>
+          <t>4.570</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>1.900</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>1.980</t>
@@ -871,17 +871,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,12 +894,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/scotland-vs-brazil/1620865469</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/tunisia-vs-netherlands/1620849622</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-24 22:00</t>
+          <t>2026-06-25 23:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -909,92 +909,92 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.000</t>
+          <t>31.000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.850</t>
+          <t>11.500</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.105</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>+2.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>1.934</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.990</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,107 +1007,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/czechia-vs-mexico/1631338312</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-londrina/1631994037</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-25 01:00</t>
+          <t>2026-06-25 23:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.780</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>5.620</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,12 +1120,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-south-korea/1620834899</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-australia/1620858183</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-25 01:00</t>
+          <t>2026-06-26 02:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1135,92 +1135,92 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.130</t>
+          <t>2.750</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.080</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>4.250</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ecuador-vs-germany/1620858182</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/turkiye-vs-usa/1631350202</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-25 20:00</t>
+          <t>2026-06-26 02:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1248,32 +1248,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Turkiye</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.290</t>
+          <t>4.190</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1298,42 +1298,42 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>1.961</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1.862</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,109 +1346,85 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/curacao-vs-ivory-coast/1631342068</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-mikkelin-palloilijat/1632011661</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-25 20:00</t>
+          <t>2026-06-26 16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Curacao</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>16.690</t>
+          <t>1.704</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.930</t>
+          <t>3.620</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.146</t>
+          <t>4.800</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1459,109 +1435,85 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/tunisia-vs-netherlands/1620849622</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-sjk-akatemia/1632011760</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-25 23:00</t>
+          <t>2026-06-26 16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21.730</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.560</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.096</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>+2.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1572,109 +1524,85 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/japan-vs-sweden/1631338310</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/brage-vs-falkenbergs/1632018127</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-25 23:00</t>
+          <t>2026-06-26 17:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.470</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.540</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.540</t>
+          <t>2.690</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>2.020</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1685,85 +1613,109 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-londrina/1631994037</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/senegal-vs-iraq/1631350200</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-25 23:30</t>
+          <t>2026-06-26 19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.227</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>6.790</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.410</t>
+          <t>12.230</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>1.990</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -1774,12 +1726,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/turkiye-vs-usa/1631350202</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-france/1631338309</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-26 02:00</t>
+          <t>2026-06-26 19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1789,47 +1741,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Turkiye</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>4.970</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.160</t>
+          <t>4.460</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1839,12 +1791,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1854,27 +1806,27 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1887,109 +1839,85 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-australia/1620858183</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-aegir/1632022567</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-26 02:00</t>
+          <t>2026-06-26 19:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>UMF Grindavik</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.780</t>
+          <t>1.751</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.240</t>
+          <t>4.140</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.220</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.699</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -2000,62 +1928,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-sjk-akatemia/1632011760</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-umf-njardvik/1632018158</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-26 16:00</t>
+          <t>2026-06-26 19:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>UMF Njardvik</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.240</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>2.830</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -2063,17 +1991,17 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -2089,47 +2017,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-mikkelin-palloilijat/1632011661</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/fylkir-vs-hk-kopavogur/1632022565</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-26 16:00</t>
+          <t>2026-06-26 19:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>1.694</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>4.220</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.830</t>
+          <t>3.970</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2139,12 +2067,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2152,17 +2080,17 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -2178,47 +2106,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/brage-vs-falkenbergs/1632018127</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-ir-reykjavik/1632022566</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-26 17:00</t>
+          <t>2026-06-26 19:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>2.540</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2228,7 +2156,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2241,17 +2169,17 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -2267,109 +2195,85 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-france/1631338309</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-vila-nova/1632022596</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00</t>
+          <t>2026-06-26 22:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.700</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.330</t>
+          <t>3.220</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.671</t>
+          <t>4.400</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2380,12 +2284,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/senegal-vs-iraq/1631350200</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/uruguay-vs-spain/1631342071</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00</t>
+          <t>2026-06-27 00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2395,92 +2299,92 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>7.510</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.820</t>
+          <t>4.170</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12.460</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2493,67 +2397,79 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-vila-nova/1632022596</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/cape-verde-vs-saudi-arabia/1631350201</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-26 22:00</t>
+          <t>2026-06-27 00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.630</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.360</t>
+          <t>2.800</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -2561,17 +2477,29 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -2582,12 +2510,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/cape-verde-vs-saudi-arabia/1631350201</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-27 00:00</t>
+          <t>2026-06-27 03:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2597,92 +2525,92 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.510</t>
+          <t>16.190</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>8.010</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.880</t>
+          <t>1.147</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+3.5</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -2695,12 +2623,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/uruguay-vs-spain/1631342071</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-27 00:00</t>
+          <t>2026-06-27 03:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2710,92 +2638,92 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7.350</t>
+          <t>2.510</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.130</t>
+          <t>2.620</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>3.930</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -2808,109 +2736,85 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ilves-vs-sjk/1631895161</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-27 03:00</t>
+          <t>2026-06-27 11:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>15.090</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7.560</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>2.820</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>+3.5</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -2921,109 +2825,85 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-osters/1632042019</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-27 03:00</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.490</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.580</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.830</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -3034,62 +2914,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ilves-vs-sjk/1631895161</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-orebro-sk/1632034515</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-27 11:00</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Orebro SK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.330</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>3.920</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.770</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -3097,17 +2977,17 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -3123,7 +3003,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-osters/1632042019</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3133,52 +3013,52 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>2.820</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -3186,17 +3066,17 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
@@ -3212,7 +3092,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-orebro-sk/1632034515</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3222,52 +3102,52 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Orebro SK</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.920</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>4.490</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -3275,17 +3155,17 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -3301,62 +3181,62 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>8.780</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>5.500</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.490</t>
+          <t>1.313</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>1.934</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>1.869</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -3364,17 +3244,17 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -3390,62 +3270,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.820</t>
+          <t>2.980</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -3453,17 +3333,17 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -3479,7 +3359,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3489,52 +3369,52 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.280</t>
+          <t>1.704</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.980</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -3542,17 +3422,17 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3568,7 +3448,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3578,52 +3458,52 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8.710</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5.420</t>
+          <t>4.210</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3631,17 +3511,17 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3682,7 +3562,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3746,7 +3626,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3761,47 +3641,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -3814,12 +3694,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3860,7 +3740,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3924,7 +3804,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3939,47 +3819,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.520</t>
+          <t>3.520</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>4.170</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3987,17 +3867,17 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -4013,7 +3893,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-vestri/1632035574</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4023,52 +3903,52 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.170</t>
+          <t>4.510</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>4.600</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -4081,7 +3961,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4102,7 +3982,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-america-mineiro/1632035579</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4112,52 +3992,52 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.210</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>4.470</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -4165,17 +4045,17 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -4191,62 +4071,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-america-mineiro/1632035579</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>3.770</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>3.360</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.470</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -4254,17 +4134,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -4305,12 +4185,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>2.610</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4320,7 +4200,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2.640</t>
+          <t>2.620</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4330,12 +4210,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -4369,7 +4249,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/volsungur-vs-grotta/1632045598</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4379,52 +4259,52 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.770</t>
+          <t>2.810</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>4.400</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -4432,17 +4312,17 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
@@ -4458,7 +4338,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4473,47 +4353,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>2.590</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.730</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.100</t>
+          <t>2.720</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -4521,17 +4401,17 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
@@ -4547,7 +4427,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4562,47 +4442,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.670</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2.650</t>
+          <t>3.120</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -4615,12 +4495,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -4661,7 +4541,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4750,7 +4630,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4839,7 +4719,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4928,22 +4808,22 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>1.641</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>3.580</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5.990</t>
+          <t>5.790</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4953,12 +4833,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
@@ -4971,12 +4851,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
@@ -5017,22 +4897,22 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.230</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5.870</t>
+          <t>5.800</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5042,12 +4922,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5077,7 +4957,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5130,22 +5010,22 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>15.480</t>
+          <t>15.310</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8.180</t>
+          <t>8.130</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>1.164</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5155,57 +5035,57 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
           <t>1.840</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>1.826</t>
         </is>
       </c>
       <c r="V48" t="inlineStr"/>
@@ -5243,22 +5123,22 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>4.250</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5268,57 +5148,57 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
         <is>
           <t>1.877</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>1.892</t>
         </is>
       </c>
       <c r="V49" t="inlineStr"/>
@@ -5356,22 +5236,22 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.751</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.230</t>
+          <t>4.240</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4.100</t>
+          <t>4.250</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5381,12 +5261,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5396,7 +5276,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5411,27 +5291,27 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
           <t>1.952</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>1.961</t>
         </is>
       </c>
       <c r="V50" t="inlineStr"/>
@@ -5469,37 +5349,37 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>13.740</t>
+          <t>14.310</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>7.400</t>
+          <t>7.570</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.189</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>+1.75</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5524,12 +5404,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5582,12 +5462,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>3.890</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5622,12 +5502,12 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5637,12 +5517,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5695,7 +5575,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5784,7 +5664,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5873,7 +5753,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-24 16:17</t>
+          <t>2026-06-25 08:53</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5962,7 +5842,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-24 16:16</t>
+          <t>2026-06-25 08:52</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6026,7 +5906,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-canada/1632123645</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6036,52 +5916,52 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.460</t>
+          <t>5.090</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4.040</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>7.640</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -6094,12 +5974,12 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S57" t="inlineStr"/>
@@ -6140,7 +6020,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6204,7 +6084,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6219,47 +6099,47 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.460</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4.020</t>
+          <t>7.640</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -6272,12 +6152,12 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
           <t>1.990</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>1.833</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
@@ -6293,12 +6173,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-06-28 21:30</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6308,32 +6188,32 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4.380</t>
+          <t>4.020</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6343,12 +6223,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -6356,17 +6236,17 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
@@ -6407,7 +6287,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6471,12 +6351,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-06-30 23:00</t>
+          <t>2026-06-28 21:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6486,47 +6366,47 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-24 16:18</t>
+          <t>2026-06-25 08:54</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2.780</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2.540</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3.330</t>
+          <t>4.490</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
@@ -6534,17 +6414,17 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S62" t="inlineStr"/>
@@ -6557,6 +6437,95 @@
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-06-30 23:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-25 08:54</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2.580</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2.570</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3.590</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2.120</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>1.751</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -580,82 +580,82 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5.500</t>
+          <t>4.650</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5.250</t>
+          <t>4.750</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.666</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>+0.75</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>+1.0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -693,22 +693,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>17.000</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.250</t>
+          <t>8.000</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>1.200</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -748,14 +748,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>2.010</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>+4.5</t>
@@ -763,7 +763,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -806,22 +806,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.550</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.570</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -919,37 +919,37 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>31.000</t>
+          <t>28.500</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>11.500</t>
+          <t>11.000</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>1.111</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+2.75</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1032,22 +1032,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.260</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.620</t>
+          <t>5.750</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.750</t>
+          <t>2.580</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>4.610</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1200,27 +1200,27 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>2.000</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1.840</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1258,22 +1258,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>3.950</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.190</t>
+          <t>4.370</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1283,57 +1283,57 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1.833</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1.961</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1371,22 +1371,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>1.719</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.620</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.800</t>
+          <t>4.870</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1396,17 +1396,29 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -1414,7 +1426,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1422,9 +1434,21 @@
           <t>2.030</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1460,22 +1484,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1490,30 +1514,54 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1549,22 +1597,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.470</t>
+          <t>2.480</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.580</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>2.700</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1574,35 +1622,59 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1613,7 +1685,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/senegal-vs-iraq/1631350200</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-france/1631338309</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1628,92 +1700,92 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.227</t>
+          <t>5.150</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.790</t>
+          <t>4.570</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12.230</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>1.892</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>1.909</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1.990</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1726,7 +1798,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-france/1631338309</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/senegal-vs-iraq/1631350200</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1741,92 +1813,92 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.970</t>
+          <t>1.225</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.460</t>
+          <t>6.830</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>12.330</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1864,17 +1936,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.140</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1889,12 +1961,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1907,12 +1979,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1953,22 +2025,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.240</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.830</t>
+          <t>2.630</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1978,12 +2050,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.729</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1991,17 +2063,17 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -2042,22 +2114,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.694</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.220</t>
+          <t>4.200</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.970</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2067,12 +2139,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2085,12 +2157,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -2131,22 +2203,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.540</t>
+          <t>2.350</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2156,12 +2228,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2220,7 +2292,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2230,7 +2302,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.220</t>
+          <t>3.230</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2245,12 +2317,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2268,7 +2340,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2309,22 +2381,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.510</t>
+          <t>7.490</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.170</t>
+          <t>4.020</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.526</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2334,12 +2406,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2349,42 +2421,42 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
           <t>1.970</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>1.806</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2422,12 +2494,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.630</t>
+          <t>2.720</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2437,7 +2509,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.800</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2447,27 +2519,27 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>2.010</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2477,12 +2549,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2492,12 +2564,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -2510,7 +2582,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2525,92 +2597,92 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>16.190</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8.010</t>
+          <t>2.640</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.147</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -2623,7 +2695,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2638,92 +2710,92 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.510</t>
+          <t>15.580</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.620</t>
+          <t>7.850</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.930</t>
+          <t>1.153</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+4.0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -2761,12 +2833,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.300</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2776,7 +2848,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.820</t>
+          <t>2.780</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2786,12 +2858,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2850,7 +2922,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2939,37 +3011,37 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3.960</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3.570</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>1.884</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>3.920</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3.570</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2982,12 +3054,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -3028,7 +3100,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3117,7 +3189,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3181,7 +3253,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3196,47 +3268,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8.780</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5.500</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.313</t>
+          <t>2.980</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -3244,17 +3316,17 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -3270,7 +3342,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3285,47 +3357,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>8.780</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>5.500</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.980</t>
+          <t>1.313</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -3333,17 +3405,17 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -3359,7 +3431,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3374,47 +3446,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>3.520</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>4.170</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -3422,17 +3494,17 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3473,7 +3545,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3562,7 +3634,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3626,7 +3698,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3641,47 +3713,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>1.704</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -3694,12 +3766,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3740,22 +3812,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.950</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3765,12 +3837,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -3783,12 +3855,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3804,7 +3876,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3819,47 +3891,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>2.540</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4.170</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3872,12 +3944,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
           <t>1.813</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1.980</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3918,22 +3990,22 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.613</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.510</t>
+          <t>4.460</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4.600</t>
+          <t>4.280</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3943,12 +4015,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -3956,17 +4028,17 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -4007,37 +4079,37 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3.330</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4.480</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>3.300</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>4.470</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -4050,12 +4122,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -4071,7 +4143,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4086,47 +4158,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Nordic United</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3.770</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -4134,17 +4206,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -4160,7 +4232,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4175,22 +4247,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nordic United</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.610</t>
+          <t>3.770</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4200,22 +4272,22 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2.620</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -4228,12 +4300,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -4274,37 +4346,37 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.810</t>
+          <t>3.090</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.400</t>
+          <t>4.380</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -4312,17 +4384,17 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
@@ -4338,7 +4410,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4353,47 +4425,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.590</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2.720</t>
+          <t>3.120</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -4406,12 +4478,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
@@ -4427,7 +4499,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4442,47 +4514,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>2.590</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3.120</t>
+          <t>2.720</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -4495,12 +4567,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -4541,7 +4613,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4630,12 +4702,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4645,7 +4717,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3.830</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4655,12 +4727,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
@@ -4673,12 +4745,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
@@ -4719,7 +4791,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4808,22 +4880,22 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>1.694</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.580</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5.790</t>
+          <t>5.440</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4833,12 +4905,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
@@ -4851,12 +4923,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
@@ -4872,7 +4944,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4887,92 +4959,92 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>15.320</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.230</t>
+          <t>8.130</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5.800</t>
+          <t>1.164</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+4.5</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -4985,7 +5057,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5000,92 +5072,92 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>15.310</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8.130</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>5.940</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>+4.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="V48" t="inlineStr"/>
@@ -5123,22 +5195,22 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>4.190</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5148,12 +5220,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5163,12 +5235,12 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5236,7 +5308,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5246,7 +5318,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.240</t>
+          <t>4.230</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5261,7 +5333,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5291,12 +5363,12 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5324,7 +5396,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5339,92 +5411,92 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14.310</t>
+          <t>3.890</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>7.570</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>2.870</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>1.649</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
           <t>2.040</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -5437,7 +5509,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5452,92 +5524,92 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3.890</t>
+          <t>14.510</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>7.680</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2.860</t>
+          <t>1.177</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1.645</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
@@ -5550,7 +5622,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5565,47 +5637,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.436</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.640</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6.340</t>
+          <t>4.020</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -5613,17 +5685,17 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S53" t="inlineStr"/>
@@ -5639,7 +5711,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5654,47 +5726,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>4.670</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4.020</t>
+          <t>6.390</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -5702,17 +5774,17 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S54" t="inlineStr"/>
@@ -5753,7 +5825,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-25 08:53</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5842,22 +5914,22 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-25 08:52</t>
+          <t>2026-06-25 19:29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>2.200</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>2.980</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5867,12 +5939,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -5885,12 +5957,12 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
@@ -5931,42 +6003,54 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>5.090</t>
+          <t>5.620</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3.540</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t>1.704</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>+0.75</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
           <t>1.793</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -5974,17 +6058,29 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
@@ -6020,7 +6116,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6109,37 +6205,37 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.460</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4.040</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>7.640</t>
+          <t>8.210</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -6147,17 +6243,17 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
           <t>1.833</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>1.990</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
@@ -6198,7 +6294,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6287,7 +6383,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6376,7 +6472,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6465,19 +6561,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-25 08:54</t>
+          <t>2026-06-25 19:30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>2.570</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>2.580</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2.570</t>
-        </is>
-      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>3.590</t>
@@ -6490,7 +6586,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6503,17 +6599,17 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="S63" t="inlineStr"/>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,107 +555,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ecuador-vs-germany/1620858182</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-mikkelin-palloilijat/1632011661</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-25 20:00</t>
+          <t>2026-06-26 16:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4.650</t>
+          <t>1.719</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.750</t>
+          <t>3.700</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.666</t>
+          <t>4.920</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,107 +668,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/curacao-vs-ivory-coast/1631342068</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-sjk-akatemia/1632011760</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-25 20:00</t>
+          <t>2026-06-26 16:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Curacao</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.000</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>1.900</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,107 +781,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/japan-vs-sweden/1631338310</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/brage-vs-falkenbergs/1632018127</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25 23:00</t>
+          <t>2026-06-26 17:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.470</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,12 +894,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/tunisia-vs-netherlands/1620849622</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-france/1631338309</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-25 23:00</t>
+          <t>2026-06-26 19:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -909,47 +909,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>28.500</t>
+          <t>4.640</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>11.000</t>
+          <t>4.730</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1.653</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+2.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -959,42 +959,42 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,107 +1007,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-londrina/1631994037</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/senegal-vs-iraq/1631350200</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-25 23:30</t>
+          <t>2026-06-26 19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>7.000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.750</t>
+          <t>12.000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>1.892</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1.917</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,47 +1120,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-australia/1620858183</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-umf-njardvik/1632018158</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-26 02:00</t>
+          <t>2026-06-26 19:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>UMF Njardvik</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.580</t>
+          <t>2.240</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.300</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.610</t>
+          <t>2.820</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1170,47 +1170,47 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,87 +1233,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/turkiye-vs-usa/1631350202</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-aegir/1632022567</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-26 02:00</t>
+          <t>2026-06-26 19:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Turkiye</t>
+          <t>UMF Grindavik</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.950</t>
+          <t>1.751</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.370</t>
+          <t>4.130</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>3.760</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>1.847</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,107 +1346,107 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-mikkelin-palloilijat/1632011661</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-ir-reykjavik/1632022566</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-26 16:00</t>
+          <t>2026-06-26 19:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>2.520</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.870</t>
+          <t>2.350</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1459,107 +1459,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-sjk-akatemia/1632011760</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/fylkir-vs-hk-kopavogur/1632022565</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-26 16:00</t>
+          <t>2026-06-26 19:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.729</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>4.180</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.540</t>
+          <t>3.830</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>1.833</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.819</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1572,107 +1572,107 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/brage-vs-falkenbergs/1632018127</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-vila-nova/1632022596</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-26 17:00</t>
+          <t>2026-06-26 22:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.580</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.700</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>1.840</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1685,12 +1685,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-france/1631338309</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/uruguay-vs-spain/1631342071</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00</t>
+          <t>2026-06-27 00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1700,92 +1700,92 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.150</t>
+          <t>6.180</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.570</t>
+          <t>3.810</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.649</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1798,12 +1798,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/senegal-vs-iraq/1631350200</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/cape-verde-vs-saudi-arabia/1631350201</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00</t>
+          <t>2026-06-27 00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1813,92 +1813,92 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.225</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6.830</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12.330</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1911,85 +1911,109 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-aegir/1632022567</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-26 19:15</t>
+          <t>2026-06-27 03:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UMF Grindavik</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>3.980</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -2000,52 +2024,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-umf-njardvik/1632018158</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-26 19:15</t>
+          <t>2026-06-27 03:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UMF Njardvik</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>16.000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>8.000</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.630</t>
+          <t>1.190</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2055,30 +2079,54 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.729</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -2089,85 +2137,109 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/fylkir-vs-hk-kopavogur/1632022565</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ilves-vs-sjk/1631895161</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-26 19:15</t>
+          <t>2026-06-27 11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:54</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.200</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>2.810</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>1.884</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2178,85 +2250,109 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-ir-reykjavik/1632022566</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-orebro-sk/1632034515</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-26 19:15</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Orebro SK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.350</t>
+          <t>3.590</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -2267,47 +2363,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-vila-nova/1632022596</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-osters/1632042019</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-26 22:00</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.230</t>
+          <t>3.570</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.400</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2317,35 +2413,59 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2356,62 +2476,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/uruguay-vs-spain/1631342071</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-27 00:00</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.490</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.020</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>4.490</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2421,12 +2541,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2436,27 +2556,27 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>+2.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2469,47 +2589,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/cape-verde-vs-saudi-arabia/1631350201</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-27 00:00</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.720</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>2.820</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2519,57 +2639,57 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -2582,47 +2702,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-27 03:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:54</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>2.280</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.640</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4.040</t>
+          <t>2.920</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2637,37 +2757,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>1.892</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2677,12 +2797,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -2695,107 +2815,107 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-27 03:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:54</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15.580</t>
+          <t>8.860</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7.850</t>
+          <t>5.580</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.153</t>
+          <t>1.306</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>+4.0</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -2808,85 +2928,109 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ilves-vs-sjk/1631895161</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-kongsvinger/1632018178</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-27 11:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-25 19:28</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.320</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.840</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.780</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -2897,85 +3041,109 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-osters/1632042019</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>2.560</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3.870</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2.420</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>1.854</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>3.570</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4.070</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>1.854</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -2986,85 +3154,109 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-orebro-sk/1632034515</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orebro SK</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>1.704</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>4.070</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4.260</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>3.960</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3.570</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -3075,85 +3267,109 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-hodd/1632018179</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.820</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -3164,85 +3380,109 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4.490</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -3253,7 +3493,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3263,75 +3503,99 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>3.360</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.980</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -3342,7 +3606,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-vestri/1632035574</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3352,75 +3616,99 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.780</t>
+          <t>1.613</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5.500</t>
+          <t>4.460</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.313</t>
+          <t>4.280</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
@@ -3431,7 +3719,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-america-mineiro/1632035579</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3441,75 +3729,99 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.170</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>4.490</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3520,62 +3832,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 15:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Nordic United</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.210</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3583,17 +3895,17 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3609,52 +3921,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-hodd/1632018179</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 15:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>3.770</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.550</t>
+          <t>3.360</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.310</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3664,30 +3976,54 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
@@ -3698,62 +4034,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/volsungur-vs-grotta/1632045598</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 15:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>4.550</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -3761,17 +4097,17 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3787,85 +4123,109 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-kongsvinger/1632018178</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.580</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>2.780</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>2.010</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
@@ -3876,85 +4236,109 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.540</t>
+          <t>2.200</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
@@ -3965,47 +4349,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-vestri/1632035574</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stromsgodset-vs-odd-bk/1632022591</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>1.606</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.460</t>
+          <t>4.480</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4.280</t>
+          <t>4.520</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4015,17 +4399,29 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -4033,17 +4429,29 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
@@ -4054,47 +4462,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-america-mineiro/1632035579</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-fc-lahti/1631904343</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 18:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.330</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.480</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4104,35 +4512,59 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
@@ -4143,85 +4575,109 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sogndal-vs-egersunds/1632024906</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-27 18:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nordic United</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.660</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>2.680</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
@@ -4232,85 +4688,109 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sao-bernardo/1632048005</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-27 19:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3.770</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>6.030</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
@@ -4321,67 +4801,79 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/volsungur-vs-grotta/1632045598</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-27 21:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.090</t>
+          <t>15.360</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.380</t>
+          <t>8.110</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.164</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>3.25</t>
@@ -4389,17 +4881,29 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>+4.5</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
@@ -4410,85 +4914,109 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-27 21:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.120</t>
+          <t>6.020</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>1.900</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
@@ -4499,67 +5027,79 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-portugal/1631338311</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-27 23:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.590</t>
+          <t>4.120</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.810</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2.720</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -4567,17 +5107,29 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
@@ -4588,85 +5140,109 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stromsgodset-vs-odd-bk/1632022591</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/dr-congo-vs-uzbekistan/1631342072</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-27 23:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.606</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.480</t>
+          <t>4.170</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.520</t>
+          <t>4.220</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
@@ -4677,85 +5253,109 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-fc-lahti/1631904343</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-27 18:00</t>
+          <t>2026-06-28 02:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>4.060</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>2.860</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.653</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+          <t>2.260</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
@@ -4766,85 +5366,109 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sogndal-vs-egersunds/1632024906</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-27 18:00</t>
+          <t>2026-06-28 02:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>14.310</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>7.660</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2.680</t>
+          <t>1.179</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
@@ -4855,85 +5479,109 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sao-bernardo/1632048005</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-27 19:00</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.694</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>4.670</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5.440</t>
+          <t>6.390</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -4944,62 +5592,62 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-27 21:00</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>15.320</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8.130</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5009,42 +5657,42 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>+4.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -5057,107 +5705,107 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-japs/1632066271</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-27 21:00</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.260</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5.940</t>
+          <t>2.810</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V48" t="inlineStr"/>
@@ -5170,107 +5818,107 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-portugal/1631338311</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-helsingborgs/1632066312</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-27 23:30</t>
+          <t>2026-06-28 15:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:55</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4.190</t>
+          <t>2.200</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.860</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.980</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="V49" t="inlineStr"/>
@@ -5283,12 +5931,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/dr-congo-vs-uzbekistan/1631342072</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-canada/1632123645</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-27 23:30</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5298,82 +5946,82 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>5.480</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.230</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>1.724</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5383,7 +6031,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V50" t="inlineStr"/>
@@ -5396,77 +6044,77 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-28 02:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3.890</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.870</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5476,22 +6124,22 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5509,74 +6157,74 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-28 02:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14.510</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7.680</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>8.210</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>1.934</t>
@@ -5584,32 +6232,32 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
@@ -5622,47 +6270,47 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4.020</t>
+          <t>3.970</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5672,35 +6320,59 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
@@ -5711,85 +6383,109 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-28 21:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.670</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6.390</t>
+          <t>4.490</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>1.813</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
@@ -5800,85 +6496,109 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-japs/1632066271</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-28 21:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2.810</t>
+          <t>4.390</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
           <t>1.800</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
@@ -5889,62 +6609,62 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-helsingborgs/1632066312</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-japan/1632130818</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-28 15:00</t>
+          <t>2026-06-29 17:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-25 19:29</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>1.746</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.670</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2.980</t>
+          <t>5.000</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t>1.917</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>1.877</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -5952,17 +6672,17 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
@@ -5978,12 +6698,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-canada/1632123645</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/netherlands-vs-morocco/1632139499</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-06-30 01:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5993,64 +6713,52 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>5.620</t>
+          <t>2.180</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
+          <t>3.280</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t>3.690</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1.704</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -6058,29 +6766,17 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
@@ -6091,12 +6787,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-06-30 23:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6106,32 +6802,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>2.570</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>2.580</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>3.590</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6141,12 +6837,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.751</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -6154,17 +6850,17 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
@@ -6180,62 +6876,62 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-07-02 00:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-25 19:30</t>
+          <t>2026-06-26 08:56</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.490</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>4.420</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>8.210</t>
+          <t>7.140</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -6248,12 +6944,12 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
@@ -6266,362 +6962,6 @@
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr"/>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-06-28 19:00</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Avai</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-06-25 19:30</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>3.380</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>4.020</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-06-28 21:30</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-06-25 19:30</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>3.310</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>4.140</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-06-28 21:30</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Goias</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-06-25 19:30</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>3.500</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4.490</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-06-30 23:00</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-06-25 19:30</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2.570</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2.580</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>3.590</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>2.110</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>1.751</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>1.757</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-mikkelin-palloilijat/1632011661</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-sjk-akatemia/1632011760</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -570,92 +570,92 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.700</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.920</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,7 +668,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-sjk-akatemia/1632011760</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-mikkelin-palloilijat/1632011661</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -683,92 +683,92 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.709</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>4.960</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -806,7 +806,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -919,37 +919,37 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.640</t>
+          <t>4.700</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.730</t>
+          <t>4.700</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.653</t>
+          <t>1.666</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -959,42 +959,42 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>1.840</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.833</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1047,22 +1047,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12.000</t>
+          <t>12.100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1072,42 +1072,42 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.240</t>
+          <t>2.230</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.550</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-aegir/1632022567</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/fylkir-vs-hk-kopavogur/1632022565</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1248,32 +1248,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UMF Grindavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1.719</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.130</t>
+          <t>4.240</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1283,27 +1283,27 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.350</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/fylkir-vs-hk-kopavogur/1632022565</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-aegir/1632022567</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1474,32 +1474,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>UMF Grindavik</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>1.746</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.180</t>
+          <t>4.160</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.830</t>
+          <t>3.770</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1524,27 +1524,27 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>1.854</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1597,37 +1597,37 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.260</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>3.930</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1637,27 +1637,27 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>1.840</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.833</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1685,7 +1685,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/uruguay-vs-spain/1631342071</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/cape-verde-vs-saudi-arabia/1631350201</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1700,52 +1700,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.180</t>
+          <t>2.690</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.810</t>
+          <t>3.430</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>2.790</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1798,7 +1798,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/cape-verde-vs-saudi-arabia/1631350201</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/uruguay-vs-spain/1631342071</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1813,92 +1813,92 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>6.450</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.700</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>1.666</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1926,92 +1926,92 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>16.000</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.660</t>
+          <t>7.800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.980</t>
+          <t>1.200</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>2.110</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+4.0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2024,7 +2024,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2039,92 +2039,92 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>16.000</t>
+          <t>2.510</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8.000</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.190</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2.140</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>2.000</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>1.877</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2162,22 +2162,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-26 08:54</t>
+          <t>2026-06-26 13:03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.300</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.860</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.810</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>4.030</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2315,12 +2315,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2388,22 +2388,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>3.590</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>4.160</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2413,27 +2413,27 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2476,7 +2476,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2491,92 +2491,92 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.490</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2589,7 +2589,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2604,92 +2604,92 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.820</t>
+          <t>4.490</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>1.847</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-26 08:54</t>
+          <t>2026-06-26 13:03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-26 08:54</t>
+          <t>2026-06-26 13:03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2928,7 +2928,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-kongsvinger/1632018178</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2943,32 +2943,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2978,57 +2978,57 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>1.806</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>1.806</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>1.909</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>1.877</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-kongsvinger/1632018178</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3056,92 +3056,92 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.560</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.870</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>3.110</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-hodd/1632018179</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3169,62 +3169,62 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3234,27 +3234,27 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3267,7 +3267,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-hodd/1632018179</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3282,92 +3282,92 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.704</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3395,47 +3395,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.690</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>3.870</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V27" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V28" t="inlineStr"/>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3832,7 +3832,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3847,70 +3847,94 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nordic United</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.660</t>
+          <t>3.830</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
@@ -3921,7 +3945,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3936,94 +3960,70 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Nordic United</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3.770</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -4261,12 +4261,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>2.190</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -4600,22 +4600,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.680</t>
+          <t>2.900</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4625,44 +4625,44 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>0</t>
@@ -4670,12 +4670,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4753,42 +4753,42 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
           <t>1.943</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>1.775</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -4801,7 +4801,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4816,92 +4816,92 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>15.360</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8.110</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>6.020</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>+4.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -4914,7 +4914,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4929,92 +4929,92 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>15.490</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>8.150</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6.020</t>
+          <t>1.162</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+4.0</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V41" t="inlineStr"/>
@@ -5027,7 +5027,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-portugal/1631338311</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/dr-congo-vs-uzbekistan/1631342072</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5042,62 +5042,62 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4.120</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.810</t>
+          <t>4.080</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>4.230</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5107,27 +5107,27 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -5140,7 +5140,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/dr-congo-vs-uzbekistan/1631342072</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-portugal/1631338311</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5155,92 +5155,92 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>4.120</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.170</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.220</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V43" t="inlineStr"/>
@@ -5253,7 +5253,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5268,47 +5268,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4.060</t>
+          <t>14.360</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>7.700</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2.860</t>
+          <t>1.178</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.653</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2.260</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5318,42 +5318,42 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V44" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5381,92 +5381,92 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14.310</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>7.660</t>
+          <t>2.190</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.179</t>
+          <t>2.910</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t>2.270</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1.671</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -5479,7 +5479,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5494,92 +5494,92 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4.670</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6.390</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
           <t>1.934</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>1.884</t>
         </is>
       </c>
       <c r="V46" t="inlineStr"/>
@@ -5592,7 +5592,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5607,47 +5607,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.416</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>4.710</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>6.530</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5657,42 +5657,42 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-26 08:55</t>
+          <t>2026-06-26 13:04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>2.190</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.670</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5893,17 +5893,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5956,22 +5956,22 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>5.480</t>
+          <t>5.440</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>1.729</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6044,7 +6044,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6059,92 +6059,92 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>8.210</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -6157,7 +6157,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6172,72 +6172,72 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>8.210</t>
+          <t>3.970</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -6247,17 +6247,17 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
@@ -6270,7 +6270,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6285,47 +6285,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3.970</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6335,42 +6335,42 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V53" t="inlineStr"/>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6634,22 +6634,22 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>1.729</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5.000</t>
+          <t>5.110</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -6677,12 +6677,12 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
@@ -6723,22 +6723,22 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2.180</t>
+          <t>2.160</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6748,12 +6748,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -6812,22 +6812,22 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2.570</t>
+          <t>2.510</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2.580</t>
+          <t>2.610</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3.590</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -6855,12 +6855,12 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-26 08:56</t>
+          <t>2026-06-26 13:05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,62 +555,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-sjk-akatemia/1632011760</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/senegal-vs-iraq/1631350200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-26 16:00</t>
+          <t>2026-06-26 19:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.259</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.670</t>
+          <t>6.750</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>11.500</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -620,42 +620,42 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>1.854</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,107 +668,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-mikkelin-palloilijat/1632011661</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-france/1631338309</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-26 16:00</t>
+          <t>2026-06-26 19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.709</t>
+          <t>7.500</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>5.650</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.960</t>
+          <t>1.400</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>1.884</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.840</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,107 +781,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/brage-vs-falkenbergs/1632018127</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/fylkir-vs-hk-kopavogur/1632022565</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26 17:00</t>
+          <t>2026-06-26 19:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-26 13:03</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.470</t>
+          <t>1.724</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>4.380</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>1.793</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,77 +894,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-france/1631338309</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-umf-njardvik/1632018158</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00</t>
+          <t>2026-06-26 19:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>UMF Njardvik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.700</t>
+          <t>2.280</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.700</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.666</t>
+          <t>2.870</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -974,27 +974,27 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,107 +1007,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/senegal-vs-iraq/1631350200</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-aegir/1632022567</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00</t>
+          <t>2026-06-26 19:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>UMF Grindavik</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>1.746</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.000</t>
+          <t>4.320</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12.100</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>-2.0</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>1.826</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1.833</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-umf-njardvik/1632018158</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-ir-reykjavik/1632022566</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,47 +1135,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UMF Njardvik</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.230</t>
+          <t>2.540</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.550</t>
+          <t>4.050</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.820</t>
+          <t>2.360</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1200,27 +1200,27 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>1.840</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1.909</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,107 +1233,107 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/fylkir-vs-hk-kopavogur/1632022565</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-vila-nova/1632022596</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-26 19:15</t>
+          <t>2026-06-26 22:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.240</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.840</t>
+          <t>3.970</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>1.934</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1.833</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,107 +1346,107 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-ir-reykjavik/1632022566</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/uruguay-vs-spain/1631342071</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-26 19:15</t>
+          <t>2026-06-27 00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.520</t>
+          <t>6.300</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>1.694</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1459,97 +1459,97 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-aegir/1632022567</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/cape-verde-vs-saudi-arabia/1631350201</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-26 19:15</t>
+          <t>2026-06-27 00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UMF Grindavik</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>2.730</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.160</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.770</t>
+          <t>2.800</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1572,67 +1572,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-vila-nova/1632022596</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-26 22:00</t>
+          <t>2026-06-27 03:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>15.000</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>7.750</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.930</t>
+          <t>1.204</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1647,32 +1647,32 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+4.5</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1685,12 +1685,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/cape-verde-vs-saudi-arabia/1631350201</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-27 00:00</t>
+          <t>2026-06-27 03:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1700,92 +1700,92 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>2.570</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.430</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.790</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1798,52 +1798,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/uruguay-vs-spain/1631342071</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ilves-vs-sjk/1631895161</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-27 00:00</t>
+          <t>2026-06-27 11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.450</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.700</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.666</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1853,52 +1853,52 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>1.892</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>1.854</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1911,57 +1911,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-osters/1632042019</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-27 03:00</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16.000</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7.800</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>4.230</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1976,42 +1976,42 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>+4.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2024,107 +2024,107 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-orebro-sk/1632034515</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-27 03:00</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Orebro SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.510</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.660</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.040</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2.140</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2137,47 +2137,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ilves-vs-sjk/1631895161</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-27 11:00</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-26 13:03</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>2.190</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.840</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2202,42 +2202,42 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2250,7 +2250,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-orebro-sk/1632034515</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2260,82 +2260,82 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orebro SK</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.729</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.030</t>
+          <t>3.810</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.590</t>
+          <t>4.550</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2345,12 +2345,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2363,107 +2363,107 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-osters/1632042019</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.590</t>
+          <t>3.740</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.160</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2476,62 +2476,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>9.140</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>5.690</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2541,42 +2541,42 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2589,107 +2589,107 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>4.200</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.490</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -2702,7 +2702,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2712,97 +2712,97 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-26 13:03</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.280</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>4.210</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.920</t>
+          <t>3.730</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>1.909</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1.806</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -2815,7 +2815,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-hodd/1632018179</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,67 +2825,67 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-26 13:03</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8.860</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5.580</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.306</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2895,27 +2895,27 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -2928,7 +2928,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2943,47 +2943,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.700</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3008,27 +3008,27 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -3066,22 +3066,22 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.110</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3154,7 +3154,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-hodd/1632018179</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3169,62 +3169,62 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>4.120</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>4.330</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3234,27 +3234,27 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3267,7 +3267,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-vestri/1632035574</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3277,52 +3277,52 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>1.613</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>4.460</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>4.280</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3332,42 +3332,42 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>1.847</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-america-mineiro/1632035579</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3390,97 +3390,97 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.870</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.320</t>
+          <t>4.560</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V27" t="inlineStr"/>
@@ -3493,109 +3493,85 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>Nordic United</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3.360</t>
+          <t>2.690</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -3606,107 +3582,107 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-vestri/1632035574</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>3.780</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.460</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4.280</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
@@ -3719,109 +3695,85 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-america-mineiro/1632035579</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/volsungur-vs-grotta/1632045598</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 15:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>4.640</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4.490</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3832,64 +3784,64 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-27 16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.830</t>
+          <t>2.210</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>3.200</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>9.5</t>
@@ -3897,7 +3849,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3912,27 +3864,27 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
           <t>1.884</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>1.952</t>
         </is>
       </c>
       <c r="V31" t="inlineStr"/>
@@ -3945,47 +3897,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-27 16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nordic United</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.660</t>
+          <t>2.610</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.330</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>2.820</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3995,35 +3947,59 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
@@ -4034,85 +4010,109 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/volsungur-vs-grotta/1632045598</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stromsgodset-vs-odd-bk/1632022591</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-27 16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>1.613</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.550</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>4.580</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
@@ -4123,12 +4123,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-fc-lahti/1631904343</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-27 18:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4138,62 +4138,62 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-26 13:03</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.580</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.780</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4203,27 +4203,27 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -4236,47 +4236,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sogndal-vs-egersunds/1632024906</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-27 18:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-26 13:03</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>2.900</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4286,57 +4286,57 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
           <t>1.884</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>1.892</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -4349,32 +4349,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stromsgodset-vs-odd-bk/1632022591</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sao-bernardo/1632048005</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-27 19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4384,72 +4384,72 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.480</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4.520</t>
+          <t>5.980</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
           <t>1.943</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>1.775</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -4462,107 +4462,107 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-fc-lahti/1631904343</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-27 18:00</t>
+          <t>2026-06-27 21:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-26 13:03</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>3.230</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>5.950</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -4575,77 +4575,77 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sogndal-vs-egersunds/1632024906</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-27 18:00</t>
+          <t>2026-06-27 21:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.130</t>
+          <t>16.350</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>8.440</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.900</t>
+          <t>1.153</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4665,17 +4665,17 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+4.0</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -4688,77 +4688,77 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sao-bernardo/1632048005</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-portugal/1631338311</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-27 19:00</t>
+          <t>2026-06-27 23:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>4.110</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>3.810</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6.030</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4768,27 +4768,27 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -4801,12 +4801,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/dr-congo-vs-uzbekistan/1631342072</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-27 21:00</t>
+          <t>2026-06-27 23:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4816,32 +4816,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6.020</t>
+          <t>4.210</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -4914,12 +4914,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-06-27 21:00</t>
+          <t>2026-06-28 02:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4929,92 +4929,92 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>15.490</t>
+          <t>14.400</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8.150</t>
+          <t>7.700</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>1.178</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>+4.0</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V41" t="inlineStr"/>
@@ -5027,12 +5027,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/dr-congo-vs-uzbekistan/1631342072</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-27 23:30</t>
+          <t>2026-06-28 02:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5042,92 +5042,92 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>3.970</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.080</t>
+          <t>2.190</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4.230</t>
+          <t>2.880</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.662</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -5140,107 +5140,107 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-portugal/1631338311</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-27 23:30</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4.120</t>
+          <t>1.409</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>4.780</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>6.600</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V43" t="inlineStr"/>
@@ -5253,107 +5253,107 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-28 02:00</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14.360</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>7.700</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.178</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
           <t>1.934</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>1.840</t>
         </is>
       </c>
       <c r="V44" t="inlineStr"/>
@@ -5366,47 +5366,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-japs/1632066271</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-28 02:00</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2.910</t>
+          <t>2.810</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5416,57 +5416,57 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1.671</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -5479,12 +5479,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-helsingborgs/1632066312</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-28 15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5494,92 +5494,92 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 17:59</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.190</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3.560</t>
+          <t>2.980</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
           <t>1.800</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="V46" t="inlineStr"/>
@@ -5592,107 +5592,107 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-canada/1632123645</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>5.440</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4.710</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6.530</t>
+          <t>1.740</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -5705,107 +5705,107 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-japs/1632066271</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2.810</t>
+          <t>8.210</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
           <t>1.775</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="V48" t="inlineStr"/>
@@ -5818,107 +5818,107 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-helsingborgs/1632066312</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-28 15:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2.980</t>
+          <t>3.970</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
           <t>1.917</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>1.769</t>
         </is>
       </c>
       <c r="V49" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-canada/1632123645</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5941,57 +5941,57 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>5.440</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6001,37 +6001,37 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
           <t>1.900</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>1.961</t>
         </is>
       </c>
       <c r="V50" t="inlineStr"/>
@@ -6044,12 +6044,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-06-28 21:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6059,82 +6059,82 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8.210</t>
+          <t>4.490</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
           <t>2.030</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -6157,12 +6157,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-06-28 21:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6172,32 +6172,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3.970</t>
+          <t>4.390</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6237,27 +6237,27 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
@@ -6270,107 +6270,107 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-japan/1632130818</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-06-29 17:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.709</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>5.200</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V53" t="inlineStr"/>
@@ -6383,109 +6383,85 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/netherlands-vs-morocco/1632139499</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-28 21:30</t>
+          <t>2026-06-30 01:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.150</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4.490</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
@@ -6496,12 +6472,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-28 21:30</t>
+          <t>2026-06-30 23:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6511,64 +6487,52 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>2.630</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4.390</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
+          <t>1.757</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -6576,29 +6540,17 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
@@ -6609,12 +6561,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-japan/1632130818</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-29 17:00</t>
+          <t>2026-07-02 00:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6624,37 +6576,37 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-26 13:05</t>
+          <t>2026-06-26 18:00</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>4.760</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5.110</t>
+          <t>8.260</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -6672,17 +6624,17 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
@@ -6695,273 +6647,6 @@
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr"/>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/netherlands-vs-morocco/1632139499</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-06-30 01:00</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-06-26 13:05</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2.160</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>3.290</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3.750</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-06-30 23:00</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-06-26 13:05</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2.510</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2.610</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3.650</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-07-02 00:00</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-06-26 13:05</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>1.490</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>4.420</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>7.140</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/fylkir-vs-hk-kopavogur/1632022565</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-aegir/1632022567</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -796,32 +796,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>UMF Grindavik</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>1.746</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.380</t>
+          <t>4.320</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -831,14 +831,14 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>11.5</t>
@@ -846,27 +846,27 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,7 +894,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-umf-njardvik/1632018158</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-ir-reykjavik/1632022566</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -909,37 +909,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UMF Njardvik</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.280</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>4.050</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.870</t>
+          <t>2.350</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -974,27 +974,27 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-aegir/1632022567</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/fylkir-vs-hk-kopavogur/1632022565</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1022,32 +1022,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UMF Grindavik</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>1.724</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.320</t>
+          <t>4.380</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.840</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1057,14 +1057,14 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>11.5</t>
@@ -1072,27 +1072,27 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>1.854</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-ir-reykjavik/1632022566</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-umf-njardvik/1632018158</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1135,47 +1135,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>UMF Njardvik</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.540</t>
+          <t>2.280</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.050</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.360</t>
+          <t>2.870</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1200,27 +1200,27 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2049,49 +2049,49 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3.870</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3.350</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>3.910</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3.410</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>1.781</t>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4148,22 +4148,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.520</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5140,7 +5140,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5155,47 +5155,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.409</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.780</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6.600</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5205,42 +5205,42 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V43" t="inlineStr"/>
@@ -5253,7 +5253,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5268,47 +5268,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.409</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>4.780</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>6.600</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5318,42 +5318,42 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V44" t="inlineStr"/>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-26 17:59</t>
+          <t>2026-06-26 18:06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5705,7 +5705,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5720,92 +5720,92 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8.210</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V48" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5931,7 +5931,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5946,92 +5946,92 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>8.210</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="V50" t="inlineStr"/>
@@ -6044,7 +6044,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6059,32 +6059,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4.490</t>
+          <t>4.390</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -6109,42 +6109,42 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
           <t>1.800</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>1.961</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -6157,7 +6157,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6172,32 +6172,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4.390</t>
+          <t>4.490</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6222,42 +6222,42 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-26 18:01</t>
+          <t>2026-06-26 18:08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-26 18:00</t>
+          <t>2026-06-26 18:07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,62 +555,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/senegal-vs-iraq/1631350200</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ilves-vs-sjk/1631895161</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00</t>
+          <t>2026-06-27 11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.259</t>
+          <t>2.260</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6.750</t>
+          <t>3.930</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.500</t>
+          <t>2.970</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -620,32 +620,32 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,107 +668,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-france/1631338309</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-osters/1632042019</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-26 19:00</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.500</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.650</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>4.160</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>2.040</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,107 +781,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-aegir/1632022567</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-orebro-sk/1632034515</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26 19:15</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UMF Grindavik</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Orebro SK</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.320</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.840</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,107 +894,107 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-ir-reykjavik/1632022566</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-26 19:15</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>1.704</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.050</t>
+          <t>3.830</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.350</t>
+          <t>4.830</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>1.892</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.840</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,72 +1007,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/fylkir-vs-hk-kopavogur/1632022565</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-26 19:15</t>
+          <t>2026-06-27 13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>2.380</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.380</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>2.930</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,47 +1120,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-umf-njardvik/1632018158</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-26 19:15</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UMF Njardvik</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.280</t>
+          <t>2.330</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.870</t>
+          <t>3.010</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1170,57 +1170,57 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>2.010</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,62 +1233,62 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-vila-nova/1632022596</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-26 22:02</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>9.120</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>5.610</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.970</t>
+          <t>1.332</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1298,42 +1298,42 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>1.806</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1.934</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,107 +1346,107 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/uruguay-vs-spain/1631342071</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-kongsvinger/1632018178</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-27 00:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.300</t>
+          <t>2.210</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.694</t>
+          <t>2.880</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1459,67 +1459,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/cape-verde-vs-saudi-arabia/1631350201</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-27 00:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.730</t>
+          <t>1.724</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.800</t>
+          <t>4.360</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1529,37 +1529,37 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1572,107 +1572,107 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/new-zealand-vs-belgium/1631338313</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-27 03:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.000</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.750</t>
+          <t>4.300</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>3.810</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>+4.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1685,107 +1685,107 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/egypt-vs-iran/1620858184</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-27 03:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.570</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>4.350</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.040</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1798,79 +1798,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ilves-vs-sjk/1631895161</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-hodd/1632018179</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-27 11:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.840</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>3</t>
@@ -1878,27 +1878,27 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1911,107 +1911,107 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-osters/1632042019</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.730</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.230</t>
+          <t>2.310</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2024,107 +2024,107 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-orebro-sk/1632034515</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-vestri/1632035574</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orebro SK</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.870</t>
+          <t>4.420</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>4.280</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2137,107 +2137,107 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-america-mineiro/1632035579</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>4.790</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>1.917</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>1.775</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2250,107 +2250,107 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-27 15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.810</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4.550</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2363,57 +2363,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Nordic United</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>2.720</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.740</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2423,47 +2423,47 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2476,109 +2476,85 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/volsungur-vs-grotta/1632045598</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.140</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.690</t>
+          <t>4.630</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -2589,107 +2565,107 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.200</t>
+          <t>3.420</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.810</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
           <t>+0.5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -2702,107 +2678,107 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.140</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.210</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.730</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -2815,12 +2791,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-hodd/1632018179</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stromsgodset-vs-odd-bk/1632022591</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2830,92 +2806,92 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>4.700</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>4.930</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -2928,107 +2904,107 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-fc-lahti/1631904343</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 18:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.700</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.740</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>2.060</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -3041,12 +3017,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-kongsvinger/1632018178</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sogndal-vs-egersunds/1632024906</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 18:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3056,22 +3032,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.160</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3081,7 +3057,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>2.970</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3091,57 +3067,57 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -3154,47 +3130,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sao-bernardo/1632048005</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 19:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1.666</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.120</t>
+          <t>3.620</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.330</t>
+          <t>5.960</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3204,57 +3180,57 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3267,107 +3243,107 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-vestri/1632035574</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 21:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.460</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4.280</t>
+          <t>5.260</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3380,107 +3356,107 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-america-mineiro/1632035579</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-27 21:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>14.740</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>8.260</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4.560</t>
+          <t>1.180</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V27" t="inlineStr"/>
@@ -3493,67 +3469,79 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-portugal/1631338311</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-27 23:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nordic United</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.550</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -3561,17 +3549,29 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -3582,107 +3582,107 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/dr-congo-vs-uzbekistan/1631342072</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-27 23:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3.780</t>
+          <t>1.628</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>4.300</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>5.610</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2.120</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
@@ -3695,85 +3695,109 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/volsungur-vs-grotta/1632045598</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-28 02:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>4.200</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.640</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>3.010</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+          <t>1.657</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3784,107 +3808,107 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-28 02:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.210</t>
+          <t>17.800</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>8.720</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3.200</t>
+          <t>1.157</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+2.25</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V31" t="inlineStr"/>
@@ -3897,72 +3921,72 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.610</t>
+          <t>1.411</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.330</t>
+          <t>4.760</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.820</t>
+          <t>6.600</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3972,32 +3996,32 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V32" t="inlineStr"/>
@@ -4010,107 +4034,107 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stromsgodset-vs-odd-bk/1632022591</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.540</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4.580</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V33" t="inlineStr"/>
@@ -4123,67 +4147,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-fc-lahti/1631904343</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-japs/1632066271</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-27 18:00</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.470</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>3.310</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>2.790</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4193,37 +4217,37 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>1.884</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -4236,47 +4260,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sogndal-vs-egersunds/1632024906</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-helsingborgs/1632066312</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-27 18:00</t>
+          <t>2026-06-28 15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.130</t>
+          <t>2.150</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.900</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4286,12 +4310,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4301,42 +4325,42 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -4349,77 +4373,77 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sao-bernardo/1632048005</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-canada/1632123645</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-27 19:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.606</t>
+          <t>5.580</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5.980</t>
+          <t>1.719</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4429,7 +4453,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4439,17 +4463,17 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -4462,57 +4486,57 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-27 21:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.230</t>
+          <t>4.360</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5.950</t>
+          <t>8.500</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4522,47 +4546,47 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -4575,62 +4599,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-27 21:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>16.350</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8.440</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.153</t>
+          <t>3.970</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4640,42 +4664,42 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>+4.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -4688,107 +4712,107 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-portugal/1631338311</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-27 23:30</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.110</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.810</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
           <t>1.900</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>1.877</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -4801,67 +4825,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/dr-congo-vs-uzbekistan/1631342072</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-27 23:30</t>
+          <t>2026-06-28 21:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4.210</t>
+          <t>4.390</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4871,37 +4895,37 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -4914,107 +4938,107 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-06-28 02:00</t>
+          <t>2026-06-28 21:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14.400</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7.700</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.178</t>
+          <t>4.490</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V41" t="inlineStr"/>
@@ -5027,12 +5051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-japan/1632130818</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-28 02:00</t>
+          <t>2026-06-29 17:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5042,92 +5066,92 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3.970</t>
+          <t>1.704</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>3.870</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2.880</t>
+          <t>5.230</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.662</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -5140,109 +5164,85 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/germany-vs-paraguay/1632164494</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-29 20:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>1.400</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4.990</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8.090</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>3.510</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3.610</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
@@ -5253,109 +5253,85 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/netherlands-vs-morocco/1632139499</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-30 01:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.409</t>
+          <t>2.180</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.780</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6.600</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
@@ -5366,57 +5342,57 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-japs/1632066271</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ivory-coast-vs-norway/1632159209</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-30 17:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2.810</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5424,21 +5400,9 @@
           <t>2.040</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -5446,29 +5410,17 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
@@ -5479,79 +5431,67 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-helsingborgs/1632066312</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-sweden/1632165856</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-28 15:00</t>
+          <t>2026-06-30 21:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-26 18:06</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>1.289</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>5.910</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.980</t>
+          <t>10.670</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>3</t>
@@ -5559,29 +5499,17 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -5592,77 +5520,77 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-canada/1632123645</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-06-30 23:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>5.440</t>
+          <t>2.410</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.740</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5672,27 +5600,27 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>+2.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -5705,87 +5633,75 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-07-02 00:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.383</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>4.940</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>8.870</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -5793,21 +5709,9 @@
           <t>2.050</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
@@ -5818,109 +5722,85 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-07-03 18:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3.970</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
+          <t>2.140</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
           <t>1.806</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
@@ -5931,87 +5811,75 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-07-03 22:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-26 18:07</t>
+          <t>2026-06-27 08:31</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.154</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>8.500</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8.210</t>
+          <t>19.650</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -6019,21 +5887,9 @@
           <t>1.833</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
@@ -6041,612 +5897,6 @@
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-06-28 21:30</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-06-26 18:07</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>3.300</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4.390</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-06-28 21:30</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Goias</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-06-26 18:07</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>3.500</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>4.490</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-japan/1632130818</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-06-29 17:00</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-06-26 18:07</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>1.709</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>3.860</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5.200</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/netherlands-vs-morocco/1632139499</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-06-30 01:00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-06-26 18:07</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2.150</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>3.300</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>3.760</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-06-30 23:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-06-26 18:08</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2.550</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2.630</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3.540</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2.110</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>1.757</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-07-02 00:00</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-06-26 18:07</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>1.413</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>4.760</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>8.260</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,107 +555,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ilves-vs-sjk/1631895161</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-27 11:00</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:44</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.260</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.930</t>
+          <t>3.810</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>1.934</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>1.909</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,12 +668,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/varbergs-bois-vs-osters/1632042019</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -683,92 +683,92 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:44</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.442</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.670</t>
+          <t>4.780</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.160</t>
+          <t>6.680</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,77 +781,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/ljungskile-vs-orebro-sk/1632034515</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-japs/1632066271</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-28 13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orebro SK</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>2.860</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,107 +894,107 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/jippo-vs-eif/1632035567</t>
+          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-helsingborgs/1632066312</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-28 15:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:44</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.704</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.830</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.830</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.769</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,107 +1007,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-ktp/1632035566</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-canada/1632123645</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-27 13:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.380</t>
+          <t>5.890</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>3.730</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.930</t>
+          <t>1.684</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>1.826</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1.763</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,47 +1120,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/hjk-helsinki-vs-kups/1631902991</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.330</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>3.080</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.010</t>
+          <t>4.100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1170,57 +1170,57 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,107 +1233,107 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ifk-mariehamn-vs-inter-turku/1631895639</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9.120</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.610</t>
+          <t>4.310</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.332</t>
+          <t>8.500</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>1.943</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1.806</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,107 +1346,107 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/haugesund-vs-kongsvinger/1632018178</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-28 19:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.210</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.880</t>
+          <t>4.080</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1459,52 +1459,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sandnes-ulf-vs-raufoss/1632024907</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-28 21:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.360</t>
+          <t>4.450</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1514,52 +1514,52 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1572,107 +1572,107 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stabaek-vs-bryne/1632018180</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-28 21:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.300</t>
+          <t>3.310</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.810</t>
+          <t>3.950</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>1.952</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.775</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1685,107 +1685,107 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/asane-fotball-vs-ranheim/1632018181</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-japan/1632130818</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-29 17:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>1.699</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.350</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>5.230</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>1.892</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1798,109 +1798,85 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-hodd/1632018179</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-aegir/1632083367</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-29 19:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>6.410</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>7.640</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1911,107 +1887,107 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/strommen-vs-moss/1632022590</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/germany-vs-paraguay/1632164494</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-29 20:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.730</t>
+          <t>1.370</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>5.180</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.310</t>
+          <t>8.650</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2024,107 +2000,107 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/throttur-reykjavik-vs-vestri/1632035574</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/netherlands-vs-morocco/1632139499</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-30 01:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.420</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.280</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
           <t>-1.0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>1.990</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2137,107 +2113,107 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/operario-ferroviario-vs-america-mineiro/1632035579</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ivory-coast-vs-norway/1632159209</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-27 14:00</t>
+          <t>2026-06-30 17:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-27 08:31</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>3.690</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3.580</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>1.840</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>3.450</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4.790</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>1.847</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>1.990</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2250,107 +2226,107 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sundsvall-vs-ostersunds-fk/1632045602</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-sweden/1632165856</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-30 21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>1.288</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>6.080</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>10.270</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>1.925</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>1.793</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2363,97 +2339,97 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/nordic-united-vs-oddevold/1632045603</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-06-30 23:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nordic United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.720</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2463,7 +2439,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2476,62 +2452,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/volsungur-vs-grotta/1632045598</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-ecuador/1632183788</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-27 15:00</t>
+          <t>2026-07-01 01:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>2.230</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.630</t>
+          <t>3.060</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2539,17 +2515,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2565,79 +2541,67 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-vps/1631895221</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/england-vs-dr-congo/1632188407</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-07-01 16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.420</t>
+          <t>5.680</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.810</t>
+          <t>12.290</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -2650,24 +2614,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -2678,32 +2630,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-jaro/1631903001</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/belgium-vs-senegal/1632188409</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-07-01 20:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2713,12 +2665,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2728,59 +2680,35 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>2.050</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2791,109 +2719,85 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/stromsgodset-vs-odd-bk/1632022591</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-27 16:00</t>
+          <t>2026-07-02 00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.700</t>
+          <t>4.940</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.930</t>
+          <t>9.240</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2904,109 +2808,85 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/ac-oulu-vs-fc-lahti/1631904343</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-asane-fotball/1632123605</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-27 18:00</t>
+          <t>2026-07-02 16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4.170</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3.680</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3.740</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3.750</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -3017,109 +2897,85 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/sogndal-vs-egersunds/1632024906</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-america-mineiro/1632130805</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-27 18:00</t>
+          <t>2026-07-02 22:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.160</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>4.640</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -3130,109 +2986,85 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sao-bernardo/1632048005</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-27 19:00</t>
+          <t>2026-07-03 15:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-27 08:31</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.666</t>
+          <t>2.200</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.620</t>
+          <t>3.220</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5.960</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
           <t>1.884</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -3243,109 +3075,85 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/croatia-vs-ghana/1631338308</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-27 21:00</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-27 08:31</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>1.591</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>4.680</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4.380</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>3.140</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5.260</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -3356,79 +3164,67 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/panama-vs-england/1631338307</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-27 21:00</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-27 08:31</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14.740</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8.260</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.180</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>3.25</t>
@@ -3436,29 +3232,17 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -3469,37 +3253,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-portugal/1631338311</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-27 23:30</t>
+          <t>2026-07-03 17:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-27 08:31</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3.540</t>
+          <t>2.790</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3509,69 +3293,45 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.210</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -3582,12 +3342,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/dr-congo-vs-uzbekistan/1631342072</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-27 23:30</t>
+          <t>2026-07-03 18:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3597,94 +3357,70 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-27 08:31</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>3.330</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.300</t>
+          <t>3.010</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5.610</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.120</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
@@ -3695,12 +3431,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/algeria-vs-austria/1631350199</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-28 02:00</t>
+          <t>2026-07-03 22:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3710,94 +3446,70 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-27 08:31</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4.200</t>
+          <t>1.150</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>8.650</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.010</t>
+          <t>20.180</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.340</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.657</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3808,109 +3520,85 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/jordan-vs-argentina/1631342069</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-28 02:00</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-27 08:31</t>
+          <t>2026-06-28 08:44</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>17.800</t>
+          <t>2.310</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8.720</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>+2.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>1.757</t>
-        </is>
-      </c>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
@@ -3921,109 +3609,85 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.411</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.760</t>
+          <t>4.090</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6.600</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
@@ -4034,109 +3698,85 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-07-04 13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>3.220</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>2.230</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
@@ -4147,109 +3787,85 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-japs/1632066271</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:44</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.470</t>
+          <t>1.621</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.310</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.790</t>
+          <t>5.070</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>1.854</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
@@ -4260,109 +3876,85 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-helsingborgs/1632066312</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-28 15:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-27 08:30</t>
+          <t>2026-06-28 08:44</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.150</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
           <t>1.990</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>1.769</t>
-        </is>
-      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
@@ -4373,109 +3965,85 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-canada/1632123645</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-27 08:31</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>5.580</t>
+          <t>6.160</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>5.040</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>1.411</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>1.800</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
@@ -4486,109 +4054,85 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-07-04 15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-27 08:31</t>
+          <t>2026-06-28 08:44</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.297</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.360</t>
+          <t>5.510</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.500</t>
+          <t>9.510</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
@@ -4599,47 +4143,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-07-04 16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-27 08:31</t>
+          <t>2026-06-28 08:45</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3.970</t>
+          <t>3.520</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4649,59 +4193,35 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
@@ -4709,1194 +4229,6 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-06-28 19:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Ceara</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>3.070</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3.960</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-06-28 21:30</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>3.300</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4.390</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-06-28 21:30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Goias</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>3.490</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>4.490</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-japan/1632130818</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-06-29 17:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>1.704</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>3.870</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5.230</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/germany-vs-paraguay/1632164494</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-06-29 20:30</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>4.990</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>8.090</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/netherlands-vs-morocco/1632139499</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-06-30 01:00</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2.180</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>3.210</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3.790</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ivory-coast-vs-norway/1632159209</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-06-30 17:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Ivory Coast</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>3.850</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>3.560</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-sweden/1632165856</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-06-30 21:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>1.289</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>5.910</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10.670</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-06-30 23:00</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2.410</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2.660</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3.790</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-07-02 00:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>1.383</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>4.940</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>8.870</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-07-03 18:00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>3.240</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>3.040</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2.530</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>2.140</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>2.100</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-07-03 22:00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Cape Verde</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-06-27 08:31</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>1.154</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>8.500</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>19.650</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,107 +555,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/landskrona-vs-varnamo/1632061616</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-japan/1632130818</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-29 17:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.729</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.810</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>5.540</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,107 +668,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/norrkoping-vs-norrby/1632061614</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-aegir/1632083367</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-29 19:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.442</t>
+          <t>1.245</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.780</t>
+          <t>6.590</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.680</t>
+          <t>7.810</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,77 +781,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/kapa-vs-japs/1632066271</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/germany-vs-paraguay/1632164494</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-28 13:00</t>
+          <t>2026-06-29 20:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>1.377</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>5.150</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.860</t>
+          <t>9.500</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -861,27 +861,27 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,47 +894,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/sweden-superettan/sandvikens-if-vs-helsingborgs/1632066312</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/netherlands-vs-morocco/1632139499</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-28 15:00</t>
+          <t>2026-06-30 01:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden - Superettan</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Helsingborgs</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>2.390</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.520</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -944,42 +944,42 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/south-africa-vs-canada/1632123645</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ivory-coast-vs-norway/1632159209</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-06-30 17:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1022,92 +1022,92 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.890</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.730</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.684</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>1.892</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>+2.5</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,107 +1120,107 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-ceara/1632056925</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-sweden/1632165856</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-06-30 21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>1.268</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.080</t>
+          <t>6.350</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.100</t>
+          <t>10.900</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-ponte-preta/1632067522</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-06-30 23:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1248,92 +1248,92 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>2.350</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.310</t>
+          <t>2.690</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8.500</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>1.826</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1.943</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,107 +1346,107 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-avai/1632066341</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-ecuador/1632183788</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-28 19:00</t>
+          <t>2026-07-01 01:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.240</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>2.910</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.080</t>
+          <t>4.110</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>1.970</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1.934</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1459,107 +1459,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-sport-recife/1632071057</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/england-vs-dr-congo/1632188407</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-28 21:30</t>
+          <t>2026-07-01 16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.283</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>5.610</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.450</t>
+          <t>12.480</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1572,107 +1572,107 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-goias/1632068424</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/belgium-vs-senegal/1632188409</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-28 21:30</t>
+          <t>2026-07-01 20:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.310</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.950</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>-0.5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1685,12 +1685,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-japan/1632130818</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-29 17:00</t>
+          <t>2026-07-02 00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1700,92 +1700,92 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>4.950</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.230</t>
+          <t>9.280</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1798,62 +1798,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-aegir/1632083367</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-asane-fotball/1632123605</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-29 19:15</t>
+          <t>2026-07-02 16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6.410</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7.640</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1861,17 +1861,17 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1887,12 +1887,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/germany-vs-paraguay/1632164494</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/spain-vs-austria/1632183191</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-29 20:30</t>
+          <t>2026-07-02 19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1902,47 +1902,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.370</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5.180</t>
+          <t>5.510</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8.650</t>
+          <t>10.840</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1952,42 +1952,42 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2000,12 +2000,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/netherlands-vs-morocco/1632139499</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-croatia/1632183795</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-30 01:00</t>
+          <t>2026-07-02 23:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2015,62 +2015,62 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.200</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.860</t>
+          <t>4.880</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2080,27 +2080,27 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2113,109 +2113,85 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ivory-coast-vs-norway/1632159209</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-america-mineiro/1632130805</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-30 17:00</t>
+          <t>2026-07-02 23:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.580</t>
+          <t>3.230</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>4.720</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2226,82 +2202,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-sweden/1632165856</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-ponte-preta/1632130814</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-30 21:00</t>
+          <t>2026-07-03 00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.288</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.080</t>
+          <t>4.670</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10.270</t>
+          <t>8.970</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2311,24 +2275,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -2339,77 +2291,77 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-algeria/1632183192</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-30 23:00</t>
+          <t>2026-07-03 03:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.660</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>4.140</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2419,27 +2371,27 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2452,62 +2404,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-ecuador/1632183788</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00</t>
+          <t>2026-07-03 15:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.230</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.060</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.860</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2515,17 +2467,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2541,52 +2493,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/england-vs-dr-congo/1632188407</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-sjk-akatemia/1632159159</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-01 16:00</t>
+          <t>2026-07-03 15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.680</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12.290</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2596,7 +2548,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2604,17 +2556,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2630,62 +2582,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/belgium-vs-senegal/1632188409</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-01 20:00</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.140</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2693,17 +2645,17 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2719,62 +2671,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.940</t>
+          <t>4.610</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>9.240</t>
+          <t>4.380</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -2782,17 +2734,17 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
@@ -2808,12 +2760,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-asane-fotball/1632123605</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-02 16:00</t>
+          <t>2026-07-03 17:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2823,47 +2775,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>2.690</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.990</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2.260</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>1.800</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>4.170</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3.680</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2871,17 +2823,17 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -2897,85 +2849,109 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-america-mineiro/1632130805</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-02 22:00</t>
+          <t>2026-07-03 18:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>3.470</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>2.910</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.640</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2.120</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -2986,85 +2962,109 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30</t>
+          <t>2026-07-03 22:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>1.161</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.220</t>
+          <t>8.230</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>19.040</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -3075,47 +3075,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-ghana/1632183796</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-04 01:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.680</t>
+          <t>4.050</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4.380</t>
+          <t>7.410</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3125,35 +3125,59 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -3164,62 +3188,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>2.990</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -3227,7 +3251,7 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3237,7 +3261,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -3253,12 +3277,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-03 17:00</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3268,47 +3292,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.790</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.210</t>
+          <t>3.120</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -3321,12 +3345,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -3342,47 +3366,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-03 18:00</t>
+          <t>2026-07-04 13:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3.330</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.010</t>
+          <t>3.220</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.230</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3392,12 +3416,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -3405,17 +3429,17 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -3431,62 +3455,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-03 22:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.150</t>
+          <t>1.653</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8.650</t>
+          <t>4.080</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20.180</t>
+          <t>4.870</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -3494,17 +3518,17 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3520,12 +3544,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3535,47 +3559,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.310</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3583,7 +3607,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3609,12 +3633,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3624,47 +3648,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>6.170</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.090</t>
+          <t>5.080</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>1.406</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -3677,12 +3701,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -3698,62 +3722,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-04 13:00</t>
+          <t>2026-07-04 15:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3.260</t>
+          <t>1.300</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.220</t>
+          <t>5.450</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2.230</t>
+          <t>9.530</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -3761,17 +3785,17 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3787,62 +3811,62 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5.070</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -3850,17 +3874,17 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3876,62 +3900,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>4.300</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3939,17 +3963,17 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3965,62 +3989,62 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.160</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5.040</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.411</t>
+          <t>4.250</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -4028,17 +4052,17 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -4054,62 +4078,62 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-04 15:00</t>
+          <t>2026-07-04 23:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44</t>
+          <t>2026-06-29 10:31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.510</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.510</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -4117,17 +4141,17 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -4143,62 +4167,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-04 16:00</t>
+          <t>2026-07-05 15:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45</t>
+          <t>2026-06-29 10:30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>4.590</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>3.870</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>1.680</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -4206,17 +4230,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -4229,6 +4253,184 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-05 17:15</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Norway - 1st Division</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Odd BK</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Haugesund</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-29 10:30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2.240</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3.900</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2.790</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-05 22:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Nautico</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-29 10:31</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2.090</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.200</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3.770</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,12 +555,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-japan/1632130818</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ivory-coast-vs-norway/1632159209</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-29 17:00</t>
+          <t>2026-06-30 17:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -570,47 +570,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5.540</t>
+          <t>2.190</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -620,42 +620,42 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,107 +668,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/afturelding-vs-aegir/1632083367</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-sweden/1632165856</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-29 19:15</t>
+          <t>2026-06-30 21:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1.303</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.590</t>
+          <t>6.000</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.810</t>
+          <t>11.000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,107 +781,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/germany-vs-paraguay/1632164494</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 20:30</t>
+          <t>2026-06-30 23:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.377</t>
+          <t>2.280</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.150</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9.500</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,12 +894,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/netherlands-vs-morocco/1632139499</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-ecuador/1632183788</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-30 01:00</t>
+          <t>2026-07-01 01:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -909,32 +909,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.390</t>
+          <t>2.310</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>2.950</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -944,57 +944,57 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ivory-coast-vs-norway/1632159209</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/england-vs-dr-congo/1632188407</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-30 17:00</t>
+          <t>2026-07-01 16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1022,92 +1022,92 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>5.560</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>13.340</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>2.040</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>1.862</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1.980</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,12 +1120,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-sweden/1632165856</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/belgium-vs-senegal/1632188409</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-30 21:00</t>
+          <t>2026-07-01 20:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1135,92 +1135,92 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.268</t>
+          <t>2.230</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.350</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.900</t>
+          <t>3.590</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>1.934</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1.869</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,107 +1233,107 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-30 23:00</t>
+          <t>2026-07-02 00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.350</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>4.890</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>9.090</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>1.833</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1.826</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1346,109 +1346,85 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-ecuador/1632183788</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-asane-fotball/1632123605</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00</t>
+          <t>2026-07-02 16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.240</t>
+          <t>1.746</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.910</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.110</t>
+          <t>3.870</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1459,12 +1435,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/england-vs-dr-congo/1632188407</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/spain-vs-austria/1632183191</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-01 16:00</t>
+          <t>2026-07-02 19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1474,32 +1450,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.283</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.610</t>
+          <t>5.300</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12.480</t>
+          <t>10.030</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1509,27 +1485,27 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1539,22 +1515,22 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1572,12 +1548,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/belgium-vs-senegal/1632188409</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-croatia/1632183795</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-01 20:00</t>
+          <t>2026-07-02 23:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1587,62 +1563,62 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>3.650</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>5.000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1652,27 +1628,27 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1685,109 +1661,85 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-america-mineiro/1632130805</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00</t>
+          <t>2026-07-02 23:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.950</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9.280</t>
+          <t>4.880</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -1798,62 +1750,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-asane-fotball/1632123605</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-ponte-preta/1632130814</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02 16:00</t>
+          <t>2026-07-03 00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.150</t>
+          <t>5.010</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>10.030</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1861,17 +1813,17 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1887,12 +1839,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/spain-vs-austria/1632183191</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-algeria/1632183192</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02 19:00</t>
+          <t>2026-07-03 03:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1902,92 +1854,92 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.308</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5.510</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10.840</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>1.980</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1.990</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2000,109 +1952,85 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-croatia/1632183795</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-sjk-akatemia/1632159159</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02 23:00</t>
+          <t>2026-07-03 15:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.880</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -2113,47 +2041,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-america-mineiro/1632130805</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02 23:00</t>
+          <t>2026-07-03 15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.230</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.720</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2163,12 +2091,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2176,17 +2104,17 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -2202,62 +2130,62 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-ponte-preta/1632130814</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-03 00:00</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.670</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.970</t>
+          <t>4.090</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.740</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2265,17 +2193,17 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -2291,109 +2219,85 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-algeria/1632183192</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-03 03:00</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.140</t>
+          <t>2.530</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2404,62 +2308,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30</t>
+          <t>2026-07-03 17:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>2.690</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4.010</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2.270</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>2.010</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>3.290</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3.760</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1.793</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2467,17 +2371,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2493,85 +2397,109 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-sjk-akatemia/1632159159</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30</t>
+          <t>2026-07-03 18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>3.440</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2.910</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2.510</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2.120</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>3.720</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3.790</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -2582,85 +2510,109 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-03 22:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>1.171</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>7.910</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>18.110</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2671,47 +2623,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-ghana/1632183796</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-04 01:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.537</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.610</t>
+          <t>3.990</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.380</t>
+          <t>7.330</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2721,35 +2673,59 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2760,62 +2736,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-03 17:00</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>2.350</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.260</t>
+          <t>2.940</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2823,17 +2799,17 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -2849,109 +2825,85 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-03 18:00</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.470</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.910</t>
+          <t>4.090</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.490</t>
+          <t>3.110</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>2.120</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -2962,109 +2914,85 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-03 22:00</t>
+          <t>2026-07-04 13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.161</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8.230</t>
+          <t>3.090</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19.040</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -3075,109 +3003,85 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-ghana/1632183796</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-04 01:30</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.680</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.050</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7.410</t>
+          <t>4.760</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -3188,12 +3092,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3203,47 +3107,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.320</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.990</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -3251,17 +3155,17 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -3277,12 +3181,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3292,47 +3196,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>5.990</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>5.010</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.120</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -3345,12 +3249,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -3366,62 +3270,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-04 13:00</t>
+          <t>2026-07-04 15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3.260</t>
+          <t>1.298</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.220</t>
+          <t>5.480</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.230</t>
+          <t>9.580</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -3429,17 +3333,17 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -3455,62 +3359,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.653</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.080</t>
+          <t>3.740</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4.870</t>
+          <t>3.520</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -3518,17 +3422,17 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3544,62 +3448,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/canada-vs-morocco/1632212030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>4.830</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3607,7 +3511,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3617,7 +3521,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3633,62 +3537,62 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6.170</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5.080</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>4.400</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -3696,17 +3600,17 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -3722,57 +3626,57 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-04 15:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.300</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5.450</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9.530</t>
+          <t>4.280</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3785,17 +3689,17 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3811,62 +3715,62 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-04 16:00</t>
+          <t>2026-07-04 23:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -3874,17 +3778,17 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3900,62 +3804,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-05 15:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>4.600</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4.300</t>
+          <t>1.689</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3968,12 +3872,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3989,62 +3893,62 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-05 17:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.240</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4.250</t>
+          <t>2.760</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -4052,17 +3956,17 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -4078,12 +3982,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-04 23:00</t>
+          <t>2026-07-05 22:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4093,32 +3997,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-29 10:31</t>
+          <t>2026-06-30 09:03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.040</t>
+          <t>3.100</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4128,12 +4032,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -4141,17 +4045,17 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -4167,62 +4071,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-05 15:30</t>
+          <t>2026-07-06 22:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-29 10:30</t>
+          <t>2026-06-30 09:03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4.590</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.870</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.680</t>
+          <t>4.350</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -4230,17 +4134,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -4253,184 +4157,6 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-07-05 17:15</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Norway - 1st Division</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Odd BK</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Haugesund</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-06-29 10:30</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2.240</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>3.900</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2.790</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-07-05 22:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-29 10:31</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>3.200</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3.770</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,12 +555,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/ivory-coast-vs-norway/1632159209</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/england-vs-dr-congo/1632188407</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-30 17:00</t>
+          <t>2026-07-01 16:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -570,92 +570,92 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>1.303</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>5.300</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>14.500</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>2.050</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,12 +668,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-sweden/1632165856</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/belgium-vs-senegal/1632188409</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-30 21:00</t>
+          <t>2026-07-01 20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -683,92 +683,92 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.303</t>
+          <t>2.210</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11.000</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,52 +781,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-crb/1632103996</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30 23:00</t>
+          <t>2026-07-02 00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-30 09:03</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.280</t>
+          <t>1.416</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>4.800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>9.000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -836,52 +836,52 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,109 +894,85 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-ecuador/1632183788</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-asane-fotball/1632123605</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-01 01:00</t>
+          <t>2026-07-02 16:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.310</t>
+          <t>1.746</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.950</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>3.870</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -1007,12 +983,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/england-vs-dr-congo/1632188407</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/spain-vs-austria/1632183191</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-01 16:00</t>
+          <t>2026-07-02 19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1022,32 +998,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.331</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.560</t>
+          <t>5.320</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13.340</t>
+          <t>10.070</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1057,29 +1033,29 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -1087,27 +1063,27 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,12 +1096,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/belgium-vs-senegal/1632188409</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-croatia/1632183795</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-01 20:00</t>
+          <t>2026-07-02 23:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1135,47 +1111,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.230</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>3.600</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.590</t>
+          <t>4.870</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1185,42 +1161,42 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,109 +1209,85 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-america-mineiro/1632130805</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00</t>
+          <t>2026-07-02 23:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.890</t>
+          <t>3.330</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9.090</t>
+          <t>4.950</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1346,62 +1298,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-asane-fotball/1632123605</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-ponte-preta/1632130814</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-02 16:00</t>
+          <t>2026-07-03 00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>1.290</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>5.180</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.870</t>
+          <t>10.490</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1409,17 +1361,17 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1435,12 +1387,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/spain-vs-austria/1632183191</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-algeria/1632183192</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-02 19:00</t>
+          <t>2026-07-03 03:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1450,92 +1402,92 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.300</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.030</t>
+          <t>4.170</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>-1.5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1548,109 +1500,85 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-croatia/1632183795</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-02 23:00</t>
+          <t>2026-07-03 15:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.650</t>
+          <t>3.320</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.000</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>1.877</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2.040</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1661,47 +1589,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-america-mineiro/1632130805</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-sjk-akatemia/1632159159</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-02 23:00</t>
+          <t>2026-07-03 15:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-30 09:03</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.880</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1711,12 +1639,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1724,17 +1652,17 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1750,62 +1678,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-ponte-preta/1632130814</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-03 00:00</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-30 09:03</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.308</t>
+          <t>2.430</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.010</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10.030</t>
+          <t>2.540</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1813,17 +1741,17 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1839,109 +1767,85 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-algeria/1632183192</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-03 03:00</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.581</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.260</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>4.070</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.729</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
           <t>1.900</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1952,62 +1856,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-sjk-akatemia/1632159159</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30</t>
+          <t>2026-07-03 17:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.690</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>3.990</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>2.260</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -2015,17 +1919,17 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -2041,85 +1945,109 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30</t>
+          <t>2026-07-03 18:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>2.910</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>2.510</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2130,85 +2058,109 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-03 22:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>8.090</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4.090</t>
+          <t>18.640</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.740</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -2219,85 +2171,109 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-ghana/1632183796</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-04 01:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.530</t>
+          <t>7.340</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2308,62 +2284,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-03 17:00</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>2.470</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2371,17 +2347,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2397,109 +2373,85 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-03 18:00</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.910</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.510</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.100</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -2510,109 +2462,85 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-03 22:00</t>
+          <t>2026-07-04 13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-30 09:03</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>3.180</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7.910</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18.110</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2623,109 +2551,85 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-ghana/1632183796</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-04 01:30</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-30 09:03</t>
+          <t>2026-07-01 09:35</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.537</t>
+          <t>1.680</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7.330</t>
+          <t>4.730</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2736,12 +2640,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2751,47 +2655,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:35</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.350</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.940</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2799,17 +2703,17 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -2825,12 +2729,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2840,47 +2744,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>6.000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.090</t>
+          <t>5.040</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.110</t>
+          <t>1.416</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2893,12 +2797,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
@@ -2914,62 +2818,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-04 13:00</t>
+          <t>2026-07-04 15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.090</t>
+          <t>5.510</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.320</t>
+          <t>9.620</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2977,17 +2881,17 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -3003,62 +2907,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.680</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4.760</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -3071,12 +2975,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
@@ -3092,47 +2996,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/canada-vs-morocco/1632212030</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>4.790</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>3.480</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3142,35 +3046,59 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -3181,62 +3109,62 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>5.990</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5.010</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>4.280</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -3244,17 +3172,17 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
           <t>1.961</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>1.826</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -3270,62 +3198,62 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-04 15:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.298</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5.480</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9.580</t>
+          <t>4.400</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>1.909</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1.943</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -3333,17 +3261,17 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -3359,62 +3287,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-crb/1632183721</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-04 16:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:37</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.750</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.740</t>
+          <t>3.060</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.520</t>
+          <t>2.750</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -3422,17 +3350,17 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3448,12 +3376,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/canada-vs-morocco/1632212030</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-france/1632241541</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-04 17:00</t>
+          <t>2026-07-04 21:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3463,47 +3391,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-30 09:03</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.830</t>
+          <t>16.380</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>7.060</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.200</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3511,17 +3439,17 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3537,12 +3465,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-04 23:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3552,47 +3480,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-30 09:03</t>
+          <t>2026-07-01 09:37</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4.400</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -3600,17 +3528,17 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -3626,62 +3554,62 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-05 15:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-30 09:03</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.370</t>
+          <t>3.830</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4.280</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -3689,17 +3617,17 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
           <t>1.854</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>1.961</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3715,47 +3643,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-04 23:00</t>
+          <t>2026-07-05 17:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-30 09:03</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.040</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>2.770</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3765,12 +3693,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -3778,17 +3706,17 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3804,62 +3732,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-norway/1632234844</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-05 15:30</t>
+          <t>2026-07-05 20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:36</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4.600</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.590</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>4.140</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3872,12 +3800,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3893,47 +3821,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-05 17:15</t>
+          <t>2026-07-05 22:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-30 09:02</t>
+          <t>2026-07-01 09:37</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.240</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2.760</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3943,12 +3871,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -3956,17 +3884,17 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3982,12 +3910,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-05 22:00</t>
+          <t>2026-07-06 22:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3997,47 +3925,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-30 09:03</t>
+          <t>2026-07-01 09:37</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.100</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>4.390</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -4050,12 +3978,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -4096,22 +4024,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-30 09:03</t>
+          <t>2026-07-01 09:37</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.350</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4121,12 +4049,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -4139,12 +4067,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -4157,6 +4085,95 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-07 23:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Operario Ferroviario</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:37</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2.410</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2.970</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3.300</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,107 +555,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/england-vs-dr-congo/1632188407</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-asane-fotball/1632123605</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01 16:00</t>
+          <t>2026-07-02 16:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.303</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5.300</t>
+          <t>4.340</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.500</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,12 +668,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/belgium-vs-senegal/1632188409</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/spain-vs-austria/1632183191</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-01 20:00</t>
+          <t>2026-07-02 19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -683,47 +683,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.210</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>5.400</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>11.100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -733,42 +733,42 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,12 +781,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-bosnia-and-herzegovina/1632139500</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-croatia/1632183795</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02 00:00</t>
+          <t>2026-07-02 23:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -796,92 +796,92 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.800</t>
+          <t>3.730</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9.000</t>
+          <t>5.130</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,85 +894,109 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-asane-fotball/1632123605</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-america-mineiro/1632130805</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-02 16:00</t>
+          <t>2026-07-02 23:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>America Mineiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.870</t>
+          <t>5.000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -983,47 +1007,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/spain-vs-austria/1632183191</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-ponte-preta/1632130814</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-02 19:00</t>
+          <t>2026-07-03 00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>1.282</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.320</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10.070</t>
+          <t>11.270</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1033,57 +1057,57 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1096,12 +1120,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-croatia/1632183795</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-algeria/1632183192</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-02 23:00</t>
+          <t>2026-07-03 03:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1111,64 +1135,64 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.600</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.870</t>
+          <t>4.370</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>1.840</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -1176,27 +1200,27 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1209,37 +1233,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-america-mineiro/1632130805</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-02 23:00</t>
+          <t>2026-07-03 15:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1249,22 +1273,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.950</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1272,17 +1296,17 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1298,62 +1322,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-ponte-preta/1632130814</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-sjk-akatemia/1632159159</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-03 00:00</t>
+          <t>2026-07-03 15:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.290</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.180</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10.490</t>
+          <t>3.560</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1366,12 +1390,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>1.943</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1.877</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1387,109 +1411,85 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-algeria/1632183192</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-03 03:00</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>4.310</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.170</t>
+          <t>4.530</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1500,62 +1500,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>2.590</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.320</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>2.390</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1563,17 +1563,17 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1589,62 +1589,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-sjk-akatemia/1632159159</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30</t>
+          <t>2026-07-03 17:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.760</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>4.020</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>2.200</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1652,17 +1652,17 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1678,85 +1678,109 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-03 18:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.430</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>2.920</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.540</t>
+          <t>2.520</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2.120</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>1.862</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1767,62 +1791,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/aegir-vs-fylkir/1632154747</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-03 19:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.581</t>
+          <t>8.500</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>6.020</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.070</t>
+          <t>1.262</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1835,12 +1859,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1856,62 +1880,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/ir-reykjavik-vs-afturelding/1632154748</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-03 17:00</t>
+          <t>2026-07-03 19:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.690</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.990</t>
+          <t>4.120</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.260</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1924,12 +1948,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -1945,47 +1969,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/grotta-vs-hk-kopavogur/1632159202</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-03 18:00</t>
+          <t>2026-07-03 19:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.910</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.510</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1995,59 +2019,35 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2.110</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2058,109 +2058,85 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-njardvik-vs-throttur-reykjavik/1632154749</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-03 22:00</t>
+          <t>2026-07-03 19:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>UMF Njardvik</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8.090</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18.640</t>
+          <t>2.560</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -2171,12 +2147,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-ghana/1632183796</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-04 01:30</t>
+          <t>2026-07-03 22:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2186,92 +2162,92 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.159</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>8.290</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7.340</t>
+          <t>19.490</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2284,85 +2260,109 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-ghana/1632183796</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-04 01:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-01 09:35</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.470</t>
+          <t>1.526</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>4.050</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>7.400</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -2373,7 +2373,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2383,37 +2383,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.470</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2436,17 +2436,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2462,62 +2462,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-04 13:00</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3.180</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.300</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2525,17 +2525,17 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2551,57 +2551,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-01 09:35</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.680</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.040</t>
+          <t>3.160</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.730</t>
+          <t>2.320</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2614,17 +2614,17 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
@@ -2640,7 +2640,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2655,47 +2655,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-01 09:35</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>1.689</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>4.020</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>4.660</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -2703,17 +2703,17 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2739,52 +2739,52 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5.040</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2792,17 +2792,17 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
@@ -2818,62 +2818,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-04 15:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>6.000</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5.510</t>
+          <t>5.040</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>9.620</t>
+          <t>1.416</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2881,17 +2881,17 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2907,62 +2907,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-04 16:00</t>
+          <t>2026-07-04 15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.303</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>5.370</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>9.610</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2970,17 +2970,17 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
@@ -2996,57 +2996,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/canada-vs-morocco/1632212030</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-04 17:00</t>
+          <t>2026-07-04 16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4.790</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.480</t>
+          <t>3.690</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>3.610</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3054,51 +3054,27 @@
           <t>1.862</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -3109,62 +3085,62 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-volsungur/1632174141</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-04 16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>1.714</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4.140</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3.940</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>1.892</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>3.370</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4.280</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -3172,17 +3148,17 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -3198,67 +3174,79 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/canada-vs-morocco/1632212030</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-04 17:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>5.200</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4.400</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -3266,17 +3254,29 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-01 09:37</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3376,62 +3376,62 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-france/1632241541</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-04 21:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>16.380</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7.060</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>4.280</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3439,12 +3439,12 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3465,12 +3465,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-04 23:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3480,47 +3480,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-01 09:37</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.040</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>4.270</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -3528,17 +3528,17 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -3554,85 +3554,109 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-france/1632241541</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-05 15:30</t>
+          <t>2026-07-04 21:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>17.440</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.830</t>
+          <t>7.170</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.191</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>+4.5</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
@@ -3643,47 +3667,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-05 17:15</t>
+          <t>2026-07-04 23:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.770</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3693,12 +3717,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -3706,17 +3730,17 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3732,62 +3756,62 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-norway/1632234844</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-05 20:00</t>
+          <t>2026-07-05 14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-01 09:36</t>
+          <t>2026-07-02 08:46</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.590</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4.140</t>
+          <t>2.770</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -3795,12 +3819,12 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3821,62 +3845,62 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-05 22:00</t>
+          <t>2026-07-05 15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-01 09:37</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>3.780</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -3884,17 +3908,17 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3910,85 +3934,109 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-norway/1632234844</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-06 22:00</t>
+          <t>2026-07-05 20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-01 09:37</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3.750</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4.080</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>3.250</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>4.390</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
@@ -3999,12 +4047,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-06 22:00</t>
+          <t>2026-07-05 23:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4014,47 +4062,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-01 09:37</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.270</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>3.460</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -4067,12 +4115,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -4088,62 +4136,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-england/1632260301</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-07 23:00</t>
+          <t>2026-07-06 00:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-01 09:37</t>
+          <t>2026-07-02 08:47</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.410</t>
+          <t>3.050</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>3.170</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>2.560</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.140</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -4156,12 +4204,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -4174,6 +4222,362 @@
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-06 22:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-02 08:47</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3.250</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4.390</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-07-06 22:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Sao Bernardo</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-02 08:47</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3.240</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3.960</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-belgium/1632265684</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FIFA - World Cup</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-02 08:47</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2.600</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3.470</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2.780</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-07-07 23:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Operario Ferroviario</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-02 08:47</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2.490</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2.940</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3.200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,107 +555,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/lyn-vs-asane-fotball/1632123605</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-02 16:00</t>
+          <t>2026-07-03 15:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.340</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.860</t>
+          <t>3.510</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>1.854</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>1.813</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,57 +668,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/spain-vs-austria/1632183191</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-sjk-akatemia/1632159159</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-02 19:00</t>
+          <t>2026-07-03 15:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.400</t>
+          <t>3.810</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11.100</t>
+          <t>3.740</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -728,47 +728,47 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>1.980</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,107 +781,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-croatia/1632183795</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02 23:00</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>2.670</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.730</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.130</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>1.909</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>1.793</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,107 +894,107 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/cuiaba-vs-america-mineiro/1632130805</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-02 23:00</t>
+          <t>2026-07-03 16:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>America Mineiro</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>4.730</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.000</t>
+          <t>5.330</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>1.819</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.775</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,107 +1007,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/fortaleza-vs-ponte-preta/1632130814</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-03 00:00</t>
+          <t>2026-07-03 17:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>2.800</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.490</t>
+          <t>4.120</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11.270</t>
+          <t>2.230</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>1.970</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,12 +1120,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-algeria/1632183192</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-03 03:00</t>
+          <t>2026-07-03 18:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1135,82 +1135,82 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>3.740</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>2.970</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.370</t>
+          <t>2.390</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1233,62 +1233,62 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/grotta-vs-hk-kopavogur/1632159202</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30</t>
+          <t>2026-07-03 19:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.330</t>
+          <t>4.230</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1296,17 +1296,17 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1322,85 +1322,109 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-sjk-akatemia/1632159159</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-njardvik-vs-throttur-reykjavik/1632154749</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30</t>
+          <t>2026-07-03 19:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>UMF Njardvik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>2.560</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.570</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2.460</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.763</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3.670</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3.560</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1411,85 +1435,109 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/ir-reykjavik-vs-afturelding/1632154748</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-03 19:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.310</t>
+          <t>4.200</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.530</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>1.826</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1500,67 +1548,79 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/aegir-vs-fylkir/1632154747</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-03 19:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.590</t>
+          <t>4.520</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>4.170</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.390</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.751</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>3.25</t>
@@ -1568,17 +1628,29 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1589,85 +1661,109 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-03 17:00</t>
+          <t>2026-07-03 22:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.760</t>
+          <t>1.162</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.020</t>
+          <t>8.650</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.200</t>
+          <t>20.000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-4.5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -1678,12 +1774,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-ghana/1632183796</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-03 18:00</t>
+          <t>2026-07-04 01:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1693,47 +1789,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.920</t>
+          <t>4.450</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.520</t>
+          <t>9.050</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1743,42 +1839,42 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1791,75 +1887,87 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/aegir-vs-fylkir/1632154747</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-03 19:15</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.500</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6.020</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.262</t>
+          <t>3.060</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1867,9 +1975,21 @@
           <t>1.840</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1880,85 +2000,109 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/ir-reykjavik-vs-afturelding/1632154748</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-03 19:15</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.120</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>3.130</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -1969,47 +2113,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/grotta-vs-hk-kopavogur/1632159202</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-03 19:15</t>
+          <t>2026-07-04 13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>3.110</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2019,35 +2163,59 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2058,85 +2226,109 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-njardvik-vs-throttur-reykjavik/1632154749</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-03 19:15</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UMF Njardvik</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>3.300</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>3.810</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.560</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -2147,79 +2339,79 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-03 22:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>1.699</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8.290</t>
+          <t>4.020</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19.490</t>
+          <t>4.610</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -2227,27 +2419,27 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2260,107 +2452,107 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-ghana/1632183796</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-04 01:30</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>6.000</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.050</t>
+          <t>5.040</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7.400</t>
+          <t>1.416</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2373,12 +2565,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-04 15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2388,70 +2580,94 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.470</t>
+          <t>1.303</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.170</t>
+          <t>5.420</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>9.490</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -2462,12 +2678,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-04 16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2477,52 +2693,64 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.240</t>
+          <t>3.720</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>3</t>
@@ -2530,17 +2758,29 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2551,85 +2791,109 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-volsungur/1632174141</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-04 13:00</t>
+          <t>2026-07-04 16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>1.645</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.160</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.320</t>
+          <t>4.240</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2640,85 +2904,109 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/canada-vs-morocco/1632212030</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 17:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>5.240</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.020</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.660</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2.060</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>1.884</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -2729,85 +3017,109 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>4.270</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -2818,52 +3130,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-crb/1632183721</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5.040</t>
+          <t>3.080</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>2.740</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2873,30 +3185,54 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -2907,85 +3243,109 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-04 15:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.303</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5.370</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9.610</t>
+          <t>4.150</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -2996,67 +3356,79 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-france/1632241541</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-04 16:00</t>
+          <t>2026-07-04 21:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>16.840</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.690</t>
+          <t>6.910</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3.610</t>
+          <t>1.202</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+1.75</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -3064,7 +3436,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3072,9 +3444,21 @@
           <t>2.000</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>+4.5</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -3085,85 +3469,109 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-volsungur/1632174141</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-04 16:00</t>
+          <t>2026-07-04 23:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>2.170</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.140</t>
+          <t>3.040</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.940</t>
+          <t>3.750</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -3174,107 +3582,107 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/canada-vs-morocco/1632212030</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-04 17:00</t>
+          <t>2026-07-05 14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5.200</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>2.770</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
@@ -3287,85 +3695,109 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-crb/1632183721</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-05 15:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:54</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.750</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.060</t>
+          <t>3.890</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.750</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3376,85 +3808,109 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-norway/1632234844</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-05 20:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>3.720</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4.310</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>3.210</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4.280</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
@@ -3465,12 +3921,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-05 23:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3480,70 +3936,94 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.120</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4.270</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>1.781</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
           <t>1.892</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
@@ -3554,12 +4034,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-france/1632241541</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-england/1632260301</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-04 21:00</t>
+          <t>2026-07-06 00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3569,92 +4049,92 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>17.440</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7.170</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
           <t>1.826</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1.862</t>
         </is>
       </c>
       <c r="V33" t="inlineStr"/>
@@ -3667,62 +4147,62 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-spain/1632283992</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-04 23:00</t>
+          <t>2026-07-06 19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>4.180</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.040</t>
+          <t>3.630</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -3730,17 +4210,17 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3756,85 +4236,109 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-05 14:00</t>
+          <t>2026-07-06 22:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-02 08:46</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.770</t>
+          <t>4.760</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1.806</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
@@ -3845,85 +4349,109 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-05 15:30</t>
+          <t>2026-07-06 22:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3.780</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
@@ -3934,12 +4462,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-norway/1632234844</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-belgium/1632265684</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-05 20:00</t>
+          <t>2026-07-07 00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3949,62 +4477,62 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>2.680</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3.430</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2.720</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>3.750</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>4.080</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4014,27 +4542,27 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -4047,12 +4575,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-05 23:30</t>
+          <t>2026-07-07 23:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4062,32 +4590,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-02 08:47</t>
+          <t>2026-07-03 08:55</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.270</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>2.940</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3.460</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4097,12 +4625,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -4110,17 +4638,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -4133,451 +4661,6 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-england/1632260301</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-07-02 08:47</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>3.050</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>3.170</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2.560</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>2.140</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-07-06 22:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Avai</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-07-02 08:47</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>3.250</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4.390</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-07-06 22:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Sao Bernardo</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-07-02 08:47</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>3.240</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3.960</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-belgium/1632265684</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-07-07 00:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-07-02 08:47</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2.600</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>3.470</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2.780</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-07-07 23:00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Operario Ferroviario</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-07-02 08:47</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2.490</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2.940</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3.200</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2.100</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,47 +555,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-jippo/1632154970</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.430</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>3.110</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -605,57 +605,57 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,92 +668,92 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/japs-vs-sjk-akatemia/1632159159</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30</t>
+          <t>2026-07-04 12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.810</t>
+          <t>3.890</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.740</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -781,107 +781,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/raufoss-vs-strommen/1632130798</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-04 13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.670</t>
+          <t>2.950</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>2.460</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.793</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,67 +894,67 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/kongsvinger-vs-sogndal/1632130796</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.751</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.730</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.330</t>
+          <t>4.630</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -964,37 +964,37 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,107 +1007,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/ranheim-vs-stabaek/1632130715</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-03 17:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.800</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.120</t>
+          <t>3.930</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.230</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2.070</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,107 +1120,107 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/australia-vs-egypt/1632164518</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-03 18:00</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.740</t>
+          <t>5.800</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.970</t>
+          <t>5.020</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.390</t>
+          <t>1.469</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/grotta-vs-hk-kopavogur/1632159202</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-vestri/1632174120</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-03 19:15</t>
+          <t>2026-07-04 14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1248,47 +1248,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>UMF Grindavik</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.630</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.230</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>2.450</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1296,17 +1296,17 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1322,107 +1322,107 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-njardvik-vs-throttur-reykjavik/1632154749</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-03 19:15</t>
+          <t>2026-07-04 15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UMF Njardvik</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.560</t>
+          <t>1.331</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.570</t>
+          <t>5.380</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.460</t>
+          <t>9.880</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.763</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1435,107 +1435,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/ir-reykjavik-vs-afturelding/1632154748</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-03 19:15</t>
+          <t>2026-07-04 16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.540</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.200</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>3.790</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>1.793</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>2.000</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1548,12 +1548,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/aegir-vs-fylkir/1632154747</t>
+          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-volsungur/1632174141</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-03 19:15</t>
+          <t>2026-07-04 16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1563,47 +1563,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.520</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.170</t>
+          <t>4.410</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>4.750</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1628,27 +1628,27 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1661,12 +1661,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-cape-verde/1632165855</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/canada-vs-morocco/1632212030</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-03 22:00</t>
+          <t>2026-07-04 17:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1676,92 +1676,92 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-03 08:55</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>5.510</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.650</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20.000</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1774,107 +1774,107 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/colombia-vs-ghana/1632183796</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-crb/1632183721</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-04 01:30</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-03 08:55</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>2.770</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.450</t>
+          <t>3.140</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9.050</t>
+          <t>2.790</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>1.833</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>1.925</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1887,62 +1887,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Gremio Novorizontino</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>3.380</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.060</t>
+          <t>4.220</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1962,17 +1962,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>1.943</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1.819</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -2000,87 +2000,87 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-04 19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.280</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.130</t>
+          <t>4.280</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2090,17 +2090,17 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2113,52 +2113,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-france/1632241541</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-04 13:00</t>
+          <t>2026-07-04 21:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.110</t>
+          <t>19.500</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>7.450</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>1.190</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2168,42 +2168,42 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+4.5</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2226,67 +2226,67 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-04 23:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Ceara</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.300</t>
+          <t>2.190</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.810</t>
+          <t>3.070</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2301,27 +2301,27 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2339,107 +2339,107 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-05 14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.020</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.610</t>
+          <t>2.710</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2452,82 +2452,82 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-05 15:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.000</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.040</t>
+          <t>3.890</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>1.934</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2542,17 +2542,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>+2.5</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2565,107 +2565,107 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-norway/1632234844</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-04 15:00</t>
+          <t>2026-07-05 20:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.303</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.420</t>
+          <t>3.790</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9.490</t>
+          <t>4.470</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>1.952</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>1.833</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -2678,107 +2678,107 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-04 16:00</t>
+          <t>2026-07-05 23:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.120</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>3.110</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.720</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>1.892</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1.840</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -2791,107 +2791,107 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-volsungur/1632174141</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-england/1632260301</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-04 16:00</t>
+          <t>2026-07-06 00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.645</t>
+          <t>3.160</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.260</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.240</t>
+          <t>2.430</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -2904,12 +2904,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/canada-vs-morocco/1632212030</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-spain/1632283992</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-04 17:00</t>
+          <t>2026-07-06 19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2919,94 +2919,70 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-03 08:55</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5.240</t>
+          <t>4.100</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -3017,12 +2993,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-06 22:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3032,32 +3008,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-03 08:55</t>
+          <t>2026-07-04 08:30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.240</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4.270</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3067,12 +3043,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3082,42 +3058,42 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -3130,12 +3106,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-crb/1632183721</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-06 22:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3145,64 +3121,64 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-03 08:55</t>
+          <t>2026-07-04 08:30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.080</t>
+          <t>3.330</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.740</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1.877</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -3210,27 +3186,27 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3243,107 +3219,107 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-belgium/1632265684</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-07 00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-03 08:55</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>2.770</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3.430</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2.630</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
           <t>1.990</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>3.190</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4.150</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
         <is>
           <t>1.925</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>1.934</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3356,12 +3332,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-france/1632241541</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-egypt/1632315073</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-04 21:00</t>
+          <t>2026-07-07 16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3371,94 +3347,70 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-03 08:55</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>16.840</t>
+          <t>1.370</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6.910</t>
+          <t>4.880</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>9.660</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>+1.75</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -3469,109 +3421,85 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-colombia/1632314983</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-04 23:00</t>
+          <t>2026-07-07 20:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-03 08:55</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.170</t>
+          <t>3.550</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.040</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.750</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -3582,47 +3510,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-05 14:00</t>
+          <t>2026-07-07 23:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>2.940</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.770</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3632,42 +3560,42 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.763</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3677,12 +3605,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
@@ -3695,12 +3623,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-japs/1632299603</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-05 15:30</t>
+          <t>2026-07-10 15:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3710,64 +3638,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-03 08:54</t>
+          <t>2026-07-04 08:29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.890</t>
+          <t>4.540</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>6.580</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -3775,29 +3691,17 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -3805,862 +3709,6 @@
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-norway/1632234844</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-07-05 20:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-03 08:55</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>3.720</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4.310</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-07-05 23:30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Nautico</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-03 08:55</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2.090</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>3.120</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3.880</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-england/1632260301</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-03 08:55</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>3.210</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>3.250</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2.420</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2.070</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-spain/1632283992</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-07-06 19:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-03 08:55</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>4.180</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>3.630</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-07-06 22:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Avai</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-07-03 08:55</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3.350</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4.760</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-07-06 22:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Sao Bernardo</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-07-03 08:55</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>3.240</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3.960</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-belgium/1632265684</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-07-07 00:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-03 08:55</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2.680</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>3.430</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2.720</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-07-07 23:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Operario Ferroviario</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-07-03 08:55</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2.490</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2.940</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3.200</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>2.100</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,97 +555,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-gnistan/1632042001</t>
+          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-05 14:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.430</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.340</t>
+          <t>3.930</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.110</t>
+          <t>2.630</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,107 +668,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/egersunds-vs-moss/1632164442</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04 12:00</t>
+          <t>2026-07-05 15:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>3.970</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.890</t>
+          <t>4.040</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.200</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>1.806</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>1.909</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.793</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,107 +781,107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/eif-vs-pk-35/1632173231</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-norway/1632234844</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-04 13:00</t>
+          <t>2026-07-05 20:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.950</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>3.760</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.460</t>
+          <t>4.690</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.769</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>1.934</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>1.970</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>1.781</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,107 +894,107 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/sjk-vs-tps/1632042025</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-05 23:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:47</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>2.330</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.010</t>
+          <t>3.010</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.630</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>1.892</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.826</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,107 +1007,107 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/jaro-vs-ilves/1632035572</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-england/1632260301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-06 00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.410</t>
+          <t>3.270</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.930</t>
+          <t>3.210</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.480</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>1.909</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1.819</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,109 +1120,85 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/hodd-vs-stromsgodset/1632164339</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-spain/1632283992</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-06 19:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.800</t>
+          <t>4.100</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.020</t>
+          <t>3.780</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>+3.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1233,85 +1209,109 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/umf-grindavik-vs-vestri/1632174120</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-04 14:00</t>
+          <t>2026-07-06 22:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UMF Grindavik</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:47</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>3.220</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.450</t>
+          <t>4.100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+          <t>1.819</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1322,62 +1322,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-ifk-mariehamn/1632042037</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-04 15:00</t>
+          <t>2026-07-06 22:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:47</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.380</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9.880</t>
+          <t>4.510</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1387,42 +1387,42 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1435,107 +1435,107 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/bryne-vs-sandnes-ulf/1632159213</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-belgium/1632265684</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-04 16:00</t>
+          <t>2026-07-07 00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:47</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>2.710</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.510</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2.640</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.925</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>1.909</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3.820</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3.790</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1548,107 +1548,107 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/leiknir-reykjavik-vs-volsungur/1632174141</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-egypt/1632315073</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-04 16:00</t>
+          <t>2026-07-07 16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:47</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.390</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.410</t>
+          <t>4.740</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.750</t>
+          <t>9.220</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.775</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>1.900</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1661,12 +1661,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/canada-vs-morocco/1632212030</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-colombia/1632314983</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-04 17:00</t>
+          <t>2026-07-07 20:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1676,92 +1676,92 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:47</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.510</t>
+          <t>3.660</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>3.100</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>2.290</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.854</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.943</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>1.840</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1.884</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1774,12 +1774,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/londrina-vs-crb/1632183721</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-07 23:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1789,92 +1789,92 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:47</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.770</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.140</t>
+          <t>2.930</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.790</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1887,12 +1887,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/gremio-novorizontino-vs-atletico-goianiense/1632183108</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ponte-preta-vs-criciuma/1632265659</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-08 23:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1902,64 +1902,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gremio Novorizontino</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:47</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>4.990</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.380</t>
+          <t>3.500</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.220</t>
+          <t>1.746</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -1967,29 +1955,17 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -2000,109 +1976,85 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/criciuma-vs-sport-recife/1632183107</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-morocco/1632336437</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-04 19:00</t>
+          <t>2026-07-09 20:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:47</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.280</t>
+          <t>3.960</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.280</t>
+          <t>6.660</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -2113,79 +2065,67 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/paraguay-vs-france/1632241541</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-japs/1632299603</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-04 21:00</t>
+          <t>2026-07-10 15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.500</t>
+          <t>1.390</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.450</t>
+          <t>4.670</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.190</t>
+          <t>6.980</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>3</t>
@@ -2193,29 +2133,17 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>+4.5</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2226,47 +2154,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/goias-vs-ceara/1632183158</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-sjk/1632154717</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-04 23:00</t>
+          <t>2026-07-10 16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceara</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-04 08:30</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.190</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.070</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.330</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2276,59 +2204,35 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+          <t>2.040</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>1.925</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -2339,109 +2243,85 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-kapa/1632299615</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-05 14:00</t>
+          <t>2026-07-10 16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>1.613</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.830</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>5.220</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -2452,79 +2332,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-hjk-helsinki/1632165923</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-05 15:30</t>
+          <t>2026-07-11 12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>3.200</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.890</t>
+          <t>3.900</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -2532,29 +2400,17 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -2565,109 +2421,85 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-norway/1632234844</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-ifk-mariehamn/1632174117</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-05 20:00</t>
+          <t>2026-07-11 14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.790</t>
+          <t>5.300</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.470</t>
+          <t>8.240</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
           <t>1.819</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
           <t>1.952</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -2678,109 +2510,85 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ac-oulu/1632173237</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-05 23:30</t>
+          <t>2026-07-11 14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-04 08:30</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.120</t>
+          <t>2.840</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.110</t>
+          <t>3.350</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.820</t>
+          <t>2.510</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+          <t>1.813</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>1.943</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -2791,109 +2599,85 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-england/1632260301</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-jippo/1632330766</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-06 00:00</t>
+          <t>2026-07-11 16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-04 08:29</t>
+          <t>2026-07-05 08:46</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3.160</t>
+          <t>5.060</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>3.800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.430</t>
+          <t>1.632</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>1.833</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2.080</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -2901,814 +2685,6 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-spain/1632283992</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-07-06 19:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-04 08:29</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>4.100</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3.680</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-07-06 22:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Sao Bernardo</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-04 08:30</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>3.240</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3.960</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-07-06 22:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Avai</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-04 08:30</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>3.330</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4.540</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>1.793</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-belgium/1632265684</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-07-07 00:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-04 08:29</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2.770</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>3.430</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2.630</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-egypt/1632315073</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-07-07 16:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-04 08:29</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>1.370</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>4.880</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>9.660</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-colombia/1632314983</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-07-07 20:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>FIFA - World Cup</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-04 08:29</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>3.550</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>3.260</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2.250</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>2.030</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>1.862</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-07-07 23:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Brazil - Serie B</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Operario Ferroviario</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-04 08:30</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2.490</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2.940</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3.200</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2.100</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1.763</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-japs/1632299603</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-07-10 15:30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Finland - Ykkosliiga</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>KTP</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>JaPS</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-04 08:29</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1.421</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>4.540</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6.580</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>1.819</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,107 +555,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/norway-1st-division/odd-bk-vs-haugesund/1632180781</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-spain/1632283992</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-05 14:00</t>
+          <t>2026-07-06 19:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>4.330</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.930</t>
+          <t>3.670</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.630</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,107 +668,107 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/mikkelin-palloilijat-vs-fc-haka/1632205928</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-05 15:30</t>
+          <t>2026-07-06 22:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.970</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.040</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>4.370</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.909</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.884</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2.080</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>1.806</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,67 +781,67 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/brazil-vs-norway/1632234844</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-05 20:00</t>
+          <t>2026-07-06 22:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.760</t>
+          <t>3.290</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.690</t>
+          <t>4.180</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -851,37 +851,37 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,62 +894,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/nautico-vs-juventude/1632193058</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-belgium/1632265684</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-05 23:30</t>
+          <t>2026-07-07 00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nautico</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-05 08:47</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.330</t>
+          <t>2.600</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.010</t>
+          <t>3.490</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -959,42 +959,42 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/mexico-vs-england/1632260301</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-egypt/1632315073</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-06 00:00</t>
+          <t>2026-07-07 16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1022,47 +1022,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.270</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.210</t>
+          <t>4.740</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.480</t>
+          <t>9.300</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.100</t>
+          <t>1.819</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,12 +1120,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-spain/1632283992</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-colombia/1632314983</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-06 19:00</t>
+          <t>2026-07-07 20:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1135,70 +1135,94 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.100</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.780</t>
+          <t>3.090</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>2.350</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>+0.25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2.110</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1.769</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>+0.5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1.909</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1.952</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1.840</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1209,12 +1233,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-06 22:00</t>
+          <t>2026-07-07 23:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1224,92 +1248,92 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-05 08:47</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.490</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.220</t>
+          <t>2.940</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.100</t>
+          <t>3.190</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>1.757</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>1.840</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1322,12 +1346,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ponte-preta-vs-criciuma/1632265659</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-06 22:00</t>
+          <t>2026-07-08 23:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1337,64 +1361,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-05 08:47</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>6.220</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.510</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1.877</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1.925</t>
-        </is>
-      </c>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -1402,29 +1414,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1.806</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
           <t>1.917</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1435,12 +1435,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-belgium/1632265684</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-morocco/1632336437</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-07 00:00</t>
+          <t>2026-07-09 20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1450,92 +1450,92 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-05 08:47</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.710</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.510</t>
+          <t>3.860</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.640</t>
+          <t>6.520</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>2.050</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>1.884</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.010</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.980</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1548,32 +1548,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-egypt/1632315073</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-japs/1632299603</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-07 16:00</t>
+          <t>2026-07-10 15:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-05 08:47</t>
+          <t>2026-07-06 10:03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.740</t>
+          <t>4.670</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9.220</t>
+          <t>6.980</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1598,59 +1598,35 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.020</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.775</t>
-        </is>
-      </c>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.900</t>
-        </is>
-      </c>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1661,109 +1637,85 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-colombia/1632314983</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-sjk/1632154717</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-07 20:00</t>
+          <t>2026-07-10 16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-05 08:47</t>
+          <t>2026-07-06 10:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.660</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.100</t>
+          <t>3.780</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.290</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1.854</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1.943</t>
-        </is>
-      </c>
+          <t>1.826</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2.110</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -1774,82 +1726,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-kapa/1632299615</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-07 23:00</t>
+          <t>2026-07-10 16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-05 08:47</t>
+          <t>2026-07-06 10:03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.613</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.930</t>
+          <t>3.830</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>5.220</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.757</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1.833</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1859,24 +1799,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.943</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
           <t>1.917</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1887,62 +1815,62 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ponte-preta-vs-criciuma/1632265659</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-hjk-helsinki/1632165923</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-08 23:00</t>
+          <t>2026-07-11 12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-05 08:47</t>
+          <t>2026-07-06 10:03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.990</t>
+          <t>3.100</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>3.880</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.746</t>
+          <t>2.130</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1950,17 +1878,17 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1976,62 +1904,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-morocco/1632336437</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/sjk-akatemia-vs-mikkelin-palloilijat/1632330722</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-09 20:00</t>
+          <t>2026-07-11 13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-05 08:47</t>
+          <t>2026-07-06 10:03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>2.800</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.960</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6.660</t>
+          <t>2.560</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -2044,12 +1972,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -2065,12 +1993,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-japs/1632299603</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-eif/1632328010</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-10 15:30</t>
+          <t>2026-07-11 13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2080,47 +2008,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.390</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.670</t>
+          <t>4.290</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.980</t>
+          <t>5.330</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2133,12 +2061,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -2154,12 +2082,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-sjk/1632154717</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-ifk-mariehamn/1632174117</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-10 16:00</t>
+          <t>2026-07-11 14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2169,47 +2097,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.710</t>
+          <t>5.340</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.330</t>
+          <t>8.350</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>2.030</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2217,17 +2145,17 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -2243,62 +2171,62 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-kapa/1632299615</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ac-oulu/1632173237</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-10 16:00</t>
+          <t>2026-07-11 14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>2.930</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.830</t>
+          <t>3.390</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5.220</t>
+          <t>2.420</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2316,7 +2244,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2332,62 +2260,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-hjk-helsinki/1632165923</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-jippo/1632330766</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 12:00</t>
+          <t>2026-07-11 16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.200</t>
+          <t>4.590</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.900</t>
+          <t>3.640</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.729</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2395,17 +2323,17 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2421,62 +2349,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-ifk-mariehamn/1632174117</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-england/1632351958</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 14:00</t>
+          <t>2026-07-11 21:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>4.180</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.300</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.240</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2484,17 +2412,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2510,62 +2438,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ac-oulu/1632173237</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-fortaleza/1632352135</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-11 14:00</t>
+          <t>2026-07-12 21:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.840</t>
+          <t>2.440</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.350</t>
+          <t>2.830</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.510</t>
+          <t>3.440</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.060</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2573,12 +2501,12 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2599,52 +2527,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-jippo/1632330766</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-goias/1632351941</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-11 16:00</t>
+          <t>2026-07-12 22:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-05 08:46</t>
+          <t>2026-07-06 10:04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5.060</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.800</t>
+          <t>3.450</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.632</t>
+          <t>3.850</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2654,7 +2582,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -2667,12 +2595,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,12 +555,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/portugal-vs-spain/1632283992</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-egypt/1632315073</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-06 19:00</t>
+          <t>2026-07-07 16:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -570,92 +570,92 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4.330</t>
+          <t>1.370</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.670</t>
+          <t>4.900</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>11.500</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.090</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.050</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,52 +668,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/botafogo-sp-vs-avai/1632212120</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-colombia/1632314983</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-06 22:00</t>
+          <t>2026-07-07 20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>3.700</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>3.150</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.370</t>
+          <t>2.300</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -723,22 +723,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -748,27 +748,27 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>2.010</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.833</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,12 +781,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/vila-nova-vs-sao-bernardo/1632212015</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-06 22:00</t>
+          <t>2026-07-07 23:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -796,92 +796,92 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Operario Ferroviario</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>2.510</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.290</t>
+          <t>2.960</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.180</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -894,109 +894,85 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/usa-vs-belgium/1632265684</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ponte-preta-vs-criciuma/1632265659</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-07 00:00</t>
+          <t>2026-07-08 23:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.600</t>
+          <t>6.220</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.490</t>
+          <t>3.680</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.850</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.070</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.060</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
+          <t>1.787</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2.050</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+          <t>1.917</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -1007,12 +983,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-egypt/1632315073</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-morocco/1632336437</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-07 16:00</t>
+          <t>2026-07-09 20:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1022,77 +998,77 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.389</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.740</t>
+          <t>3.910</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9.300</t>
+          <t>6.560</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2.080</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1102,12 +1078,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1120,109 +1096,85 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-colombia/1632314983</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-japs/1632299603</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-07 20:00</t>
+          <t>2026-07-10 15:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.530</t>
+          <t>1.350</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.090</t>
+          <t>4.830</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.350</t>
+          <t>7.780</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.970</t>
-        </is>
-      </c>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.769</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1233,82 +1185,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-sjk/1632154717</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-07 23:00</t>
+          <t>2026-07-10 16:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.490</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.940</t>
+          <t>3.820</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.190</t>
+          <t>3.520</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.757</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.961</t>
-        </is>
-      </c>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1318,24 +1258,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1.970</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1.787</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1346,62 +1274,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ponte-preta-vs-criciuma/1632265659</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-kapa/1632299615</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-08 23:00</t>
+          <t>2026-07-10 16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:31</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.220</t>
+          <t>1.613</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>3.830</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>5.220</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1409,12 +1337,12 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1435,12 +1363,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-morocco/1632336437</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/spain-vs-belgium/1632370821</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-09 20:00</t>
+          <t>2026-07-10 19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1450,67 +1378,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.628</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.860</t>
+          <t>4.010</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.520</t>
+          <t>5.740</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.869</t>
-        </is>
-      </c>
+          <t>2.100</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1520,24 +1436,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1.847</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.917</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
+          <t>1.840</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1548,62 +1452,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-japs/1632299603</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/juventude-vs-vila-nova/1632307207</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-10 15:30</t>
+          <t>2026-07-10 22:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-06 10:03</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.390</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.670</t>
+          <t>3.260</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.980</t>
+          <t>4.790</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1611,17 +1515,17 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1637,47 +1541,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-sjk/1632154717</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sport-recife-vs-botafogo-sp/1632307210</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-10 16:00</t>
+          <t>2026-07-10 23:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-06 10:03</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.780</t>
+          <t>3.400</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.400</t>
+          <t>4.100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1687,12 +1591,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1700,17 +1604,17 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1726,62 +1630,62 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-kapa/1632299615</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-hjk-helsinki/1632165923</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-10 16:00</t>
+          <t>2026-07-11 12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-06 10:03</t>
+          <t>2026-07-07 09:31</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>3.110</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.830</t>
+          <t>3.770</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.220</t>
+          <t>2.160</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.800</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1789,17 +1693,17 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1815,47 +1719,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/fc-lahti-vs-hjk-helsinki/1632165923</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/sjk-akatemia-vs-mikkelin-palloilijat/1632330722</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-11 12:00</t>
+          <t>2026-07-11 13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>SJK Akatemia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Mikkelin Palloilijat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-06 10:03</t>
+          <t>2026-07-07 09:31</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3.100</t>
+          <t>2.920</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.880</t>
+          <t>3.250</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.130</t>
+          <t>2.410</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1865,12 +1769,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>1.751</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>2.080</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1878,17 +1782,17 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1904,7 +1808,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/sjk-akatemia-vs-mikkelin-palloilijat/1632330722</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-eif/1632328010</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1919,47 +1823,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-06 10:03</t>
+          <t>2026-07-07 09:31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.800</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>4.290</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.560</t>
+          <t>5.330</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.900</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1967,17 +1871,17 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.952</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -1993,62 +1897,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/fc-haka-vs-eif/1632328010</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-ifk-mariehamn/1632174117</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-11 13:00</t>
+          <t>2026-07-11 14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-06 10:03</t>
+          <t>2026-07-07 09:31</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.314</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.290</t>
+          <t>5.490</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.330</t>
+          <t>8.740</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.961</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.892</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2061,12 +1965,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -2082,7 +1986,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/gnistan-vs-ifk-mariehamn/1632174117</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ac-oulu/1632173237</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2097,47 +2001,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-06 10:03</t>
+          <t>2026-07-07 09:31</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>2.910</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.340</t>
+          <t>3.340</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.350</t>
+          <t>2.460</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.030</t>
+          <t>2.110</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -2145,17 +2049,17 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.917</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -2171,62 +2075,62 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/tps-vs-ac-oulu/1632173237</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-jippo/1632330766</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-11 14:00</t>
+          <t>2026-07-11 16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>HJK Klubi 04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-06 10:03</t>
+          <t>2026-07-07 09:31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.930</t>
+          <t>4.430</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.390</t>
+          <t>3.620</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>1.757</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -2239,12 +2143,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>1.925</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>1.862</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2260,85 +2164,109 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/hjk-klubi-04-vs-jippo/1632330766</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-england/1632351958</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-11 16:00</t>
+          <t>2026-07-11 21:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-06 10:03</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.590</t>
+          <t>4.260</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.640</t>
+          <t>3.710</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.840</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>1.961</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>2.000</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1.892</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>1.952</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>1.840</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1.847</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -2349,62 +2277,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/norway-vs-england/1632351958</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/sao-bernardo-vs-cuiaba/1632352108</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-11 21:00</t>
+          <t>2026-07-12 19:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.180</t>
+          <t>2.340</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>2.990</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>3.410</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1.854</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2412,17 +2340,17 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
@@ -2438,12 +2366,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-fortaleza/1632352135</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/avai-vs-nautico/1632352109</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-12 21:00</t>
+          <t>2026-07-12 19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2453,42 +2381,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Atletico Goianiense</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nautico</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.440</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.830</t>
+          <t>2.900</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.440</t>
+          <t>2.660</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2506,12 +2434,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1.980</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2527,12 +2455,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-goias/1632351941</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/atletico-goianiense-vs-fortaleza/1632352135</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-12 22:00</t>
+          <t>2026-07-12 21:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2542,47 +2470,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atletico Goianiense</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-06 10:04</t>
+          <t>2026-07-07 09:32</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.970</t>
+          <t>2.380</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.450</t>
+          <t>2.850</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.850</t>
+          <t>3.530</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -2590,17 +2518,17 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.990</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.943</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
@@ -2613,6 +2541,184 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/crb-vs-goias/1632351941</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Goias</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-07 09:32</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.450</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3.850</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1.980</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1.862</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1.990</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1.833</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/america-mineiro-vs-londrina/1632366416</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brazil - Serie B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>America Mineiro</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-07 09:32</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.961</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3.590</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3.720</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1.970</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1.869</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1.800</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2.030</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/pinnacle_odds_data.xlsx
+++ b/outputs/pinnacle_odds_data.xlsx
@@ -555,97 +555,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/argentina-vs-egypt/1632315073</t>
+          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ponte-preta-vs-criciuma/1632265659</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-07 16:00</t>
+          <t>2026-07-08 23:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Brazil - Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-07 09:32</t>
+          <t>2026-07-08 08:16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.370</t>
+          <t>5.720</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.900</t>
+          <t>3.540</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.500</t>
+          <t>1.689</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>+0.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.090</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>1.934</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>1.970</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.877</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.884</t>
+          <t>1.787</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -668,12 +668,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/switzerland-vs-colombia/1632314983</t>
+          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-morocco/1632336437</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-07 20:00</t>
+          <t>2026-07-09 20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -683,47 +683,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-07 09:32</t>
+          <t>2026-07-08 08:16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.700</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.150</t>
+          <t>3.840</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.300</t>
+          <t>6.420</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.980</t>
+          <t>2.100</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>1.826</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -733,42 +733,42 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1.775</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.847</t>
+          <t>2.020</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.010</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.840</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>+0.5</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1.806</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>1.990</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -781,109 +781,85 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/athletic-club-vs-operario-ferroviario/1632235775</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/ktp-vs-japs/1632299603</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07 23:00</t>
+          <t>2026-07-10 15:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Operario Ferroviario</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-07 09:32</t>
+          <t>2026-07-08 08:16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.510</t>
+          <t>1.334</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.960</t>
+          <t>4.960</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>7.980</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.110</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.781</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.980</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.813</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.892</t>
+          <t>1.793</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1.952</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1.892</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>1.826</t>
-        </is>
-      </c>
+          <t>2.010</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -894,62 +870,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/ponte-preta-vs-criciuma/1632265659</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/vps-vs-sjk/1632154717</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-08 23:00</t>
+          <t>2026-07-10 16:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil - Serie B</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-07 09:32</t>
+          <t>2026-07-08 08:15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.220</t>
+          <t>2.050</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.680</t>
+          <t>3.770</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>3.370</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>+0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.070</t>
+          <t>2.060</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1.813</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -957,17 +933,17 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.900</t>
+          <t>1.847</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -983,109 +959,85 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/france-vs-morocco/1632336437</t>
+          <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/pk-35-vs-kapa/1632299615</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-09 20:00</t>
+          <t>2026-07-10 16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FIFA - World Cup</t>
+          <t>Finland - Ykkosliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>PK-35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-07 09:32</t>
+          <t>2026-07-08 08:16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.613</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.910</t>
+          <t>3.830</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.560</t>
+          <t>5.220</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.040</t>
+          <t>1.800</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>1.869</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1.990</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.800</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <